--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B6ADA16-A72E-4BC9-B56E-4DDCBB576DF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5697BD62-E239-41CC-8916-076D7B08E19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="87">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -295,6 +295,9 @@
   </si>
   <si>
     <t>superb day.</t>
+  </si>
+  <si>
+    <t>holiday.</t>
   </si>
 </sst>
 </file>
@@ -2316,26 +2319,50 @@
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15" t="str">
+      <c r="A33" s="8">
+        <v>46278</v>
+      </c>
+      <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>75</v>
+      </c>
+      <c r="D33" s="14">
+        <v>420</v>
+      </c>
+      <c r="E33" s="14">
+        <v>280</v>
+      </c>
+      <c r="F33" s="14">
+        <v>0</v>
+      </c>
+      <c r="G33" s="14">
+        <v>0</v>
+      </c>
+      <c r="H33" s="14">
+        <v>70</v>
+      </c>
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J33" s="15" t="str">
+        <v>1325</v>
+      </c>
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K33" s="16"/>
-      <c r="L33" s="16"/>
-      <c r="M33" s="16"/>
-      <c r="N33" s="17"/>
+        <v>115</v>
+      </c>
+      <c r="K33" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L33" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M33" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N33" s="17" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5697BD62-E239-41CC-8916-076D7B08E19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB449C56-0419-42D1-8404-BB9714C10AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -298,6 +298,9 @@
   </si>
   <si>
     <t>holiday.</t>
+  </si>
+  <si>
+    <t>busy day.</t>
   </si>
 </sst>
 </file>
@@ -2365,26 +2368,50 @@
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="13"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15" t="str">
+      <c r="A34" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B34" s="14">
+        <v>420</v>
+      </c>
+      <c r="C34" s="14">
+        <v>45</v>
+      </c>
+      <c r="D34" s="14">
+        <v>180</v>
+      </c>
+      <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>240</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
+        <v>180</v>
+      </c>
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J34" s="15" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K34" s="16"/>
-      <c r="L34" s="16"/>
-      <c r="M34" s="16"/>
-      <c r="N34" s="17"/>
+        <v>255</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L34" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M34" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N34" s="17" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB449C56-0419-42D1-8404-BB9714C10AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FBA78E-63C0-4C6A-97DA-E3E958E6BC9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -301,6 +301,9 @@
   </si>
   <si>
     <t>busy day.</t>
+  </si>
+  <si>
+    <t>calm day.</t>
   </si>
 </sst>
 </file>
@@ -2414,26 +2417,50 @@
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15" t="str">
+      <c r="A35" s="8">
+        <v>46280</v>
+      </c>
+      <c r="B35" s="14">
+        <v>400</v>
+      </c>
+      <c r="C35" s="14">
+        <v>90</v>
+      </c>
+      <c r="D35" s="14">
+        <v>120</v>
+      </c>
+      <c r="E35" s="14">
+        <v>180</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
+        <v>120</v>
+      </c>
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J35" s="15" t="str">
+        <v>1210</v>
+      </c>
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K35" s="16"/>
-      <c r="L35" s="16"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="17"/>
+        <v>230</v>
+      </c>
+      <c r="K35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L35" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M35" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N35" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FBA78E-63C0-4C6A-97DA-E3E958E6BC9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0156D71-94CC-4BF7-ADE3-B56FAA593647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="89">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2463,26 +2463,50 @@
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15" t="str">
+      <c r="A36" s="8">
+        <v>46281</v>
+      </c>
+      <c r="B36" s="14">
+        <v>390</v>
+      </c>
+      <c r="C36" s="14">
+        <v>45</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
+        <v>60</v>
+      </c>
+      <c r="F36" s="14">
+        <v>180</v>
+      </c>
+      <c r="G36" s="14">
+        <v>3</v>
+      </c>
+      <c r="H36" s="14">
+        <v>210</v>
+      </c>
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J36" s="15" t="str">
+        <v>1065</v>
+      </c>
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16"/>
-      <c r="N36" s="17"/>
+        <v>375</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L36" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M36" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N36" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0156D71-94CC-4BF7-ADE3-B56FAA593647}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C4296-03EB-4D50-BC12-804B7F491C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="91">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -304,6 +304,12 @@
   </si>
   <si>
     <t>calm day.</t>
+  </si>
+  <si>
+    <t>good day.</t>
+  </si>
+  <si>
+    <t>hectic day.</t>
   </si>
 </sst>
 </file>
@@ -954,7 +960,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N401"/>
+  <dimension ref="A1:N405"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1084,7 +1090,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B6" s="9">
         <v>420</v>
@@ -1099,21 +1105,21 @@
         <v>90</v>
       </c>
       <c r="F6" s="9">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G6" s="9">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H6" s="9">
         <v>60</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I69" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>795</v>
+        <f t="shared" ref="I6:I73" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
+        <v>1095</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J69" si="1">IF(I6="","",1440-I6)</f>
-        <v>645</v>
+        <f t="shared" ref="J6:J73" si="1">IF(I6="","",1440-I6)</f>
+        <v>345</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -1130,1493 +1136,1611 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
+        <v>46248</v>
+      </c>
+      <c r="B7" s="9">
+        <v>380</v>
+      </c>
+      <c r="C7" s="9">
+        <v>35</v>
+      </c>
+      <c r="D7" s="9">
+        <v>120</v>
+      </c>
+      <c r="E7" s="9">
+        <v>60</v>
+      </c>
+      <c r="F7" s="9">
+        <v>300</v>
+      </c>
+      <c r="G7" s="9">
+        <v>5</v>
+      </c>
+      <c r="H7" s="9">
+        <v>120</v>
+      </c>
+      <c r="I7" s="10">
+        <f t="shared" si="0"/>
+        <v>1015</v>
+      </c>
+      <c r="J7" s="10">
+        <f t="shared" si="1"/>
+        <v>425</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N7" s="12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="8">
+        <v>46249</v>
+      </c>
+      <c r="B8" s="9">
+        <v>400</v>
+      </c>
+      <c r="C8" s="9">
+        <v>60</v>
+      </c>
+      <c r="D8" s="9">
+        <v>210</v>
+      </c>
+      <c r="E8" s="9">
+        <v>45</v>
+      </c>
+      <c r="F8" s="9">
+        <v>360</v>
+      </c>
+      <c r="G8" s="9">
+        <v>6</v>
+      </c>
+      <c r="H8" s="9">
+        <v>30</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="0"/>
+        <v>1105</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" si="1"/>
+        <v>335</v>
+      </c>
+      <c r="K8" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="8">
+        <v>46250</v>
+      </c>
+      <c r="B9" s="9">
+        <v>380</v>
+      </c>
+      <c r="C9" s="9">
+        <v>45</v>
+      </c>
+      <c r="D9" s="9">
+        <v>180</v>
+      </c>
+      <c r="E9" s="9">
+        <v>35</v>
+      </c>
+      <c r="F9" s="9">
+        <v>420</v>
+      </c>
+      <c r="G9" s="9">
+        <v>7</v>
+      </c>
+      <c r="H9" s="9">
+        <v>60</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="J9" s="10">
+        <f t="shared" si="1"/>
+        <v>320</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="N9" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="8">
+        <v>46251</v>
+      </c>
+      <c r="B10" s="9">
+        <v>420</v>
+      </c>
+      <c r="C10" s="9">
+        <v>45</v>
+      </c>
+      <c r="D10" s="9">
+        <v>180</v>
+      </c>
+      <c r="E10" s="9">
+        <v>90</v>
+      </c>
+      <c r="F10" s="9">
+        <v>0</v>
+      </c>
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
+        <v>60</v>
+      </c>
+      <c r="I10" s="10">
+        <v>795</v>
+      </c>
+      <c r="J10" s="10">
+        <v>645</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="N10" s="12" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="8">
         <v>46252</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B11" s="14">
         <v>450</v>
       </c>
-      <c r="C7" s="14">
+      <c r="C11" s="14">
         <v>30</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D11" s="14">
         <v>150</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E11" s="14">
         <v>120</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F11" s="14">
         <v>420</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G11" s="14">
         <v>6</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H11" s="14">
         <v>45</v>
       </c>
-      <c r="I7" s="15">
+      <c r="I11" s="15">
         <f t="shared" si="0"/>
         <v>1215</v>
       </c>
-      <c r="J7" s="15">
+      <c r="J11" s="15">
         <f t="shared" si="1"/>
         <v>225</v>
       </c>
-      <c r="K7" s="16" t="s">
+      <c r="K11" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L11" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M11" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="17" t="s">
+      <c r="N11" s="17" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" s="8">
         <v>46253</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B12" s="14">
         <v>480</v>
       </c>
-      <c r="C8" s="14">
+      <c r="C12" s="14">
         <v>40</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D12" s="14">
         <v>120</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E12" s="14">
         <v>100</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F12" s="14">
         <v>420</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G12" s="14">
         <v>7</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H12" s="14">
         <v>30</v>
       </c>
-      <c r="I8" s="15">
+      <c r="I12" s="15">
         <f t="shared" si="0"/>
         <v>1190</v>
       </c>
-      <c r="J8" s="15">
+      <c r="J12" s="15">
         <f t="shared" si="1"/>
         <v>250</v>
       </c>
-      <c r="K8" s="16" t="s">
+      <c r="K12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L8" s="16" t="s">
+      <c r="L12" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M8" s="16" t="s">
+      <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N8" s="17" t="s">
+      <c r="N12" s="17" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A9" s="8">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" s="8">
         <v>46254</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B13" s="14">
         <v>450</v>
       </c>
-      <c r="C9" s="14">
+      <c r="C13" s="14">
         <v>30</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D13" s="14">
         <v>150</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E13" s="14">
         <v>120</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F13" s="14">
         <v>240</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G13" s="14">
         <v>4</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H13" s="14">
         <v>45</v>
       </c>
-      <c r="I9" s="15">
+      <c r="I13" s="15">
         <f t="shared" si="0"/>
         <v>1035</v>
       </c>
-      <c r="J9" s="15">
+      <c r="J13" s="15">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="K9" s="16" t="s">
+      <c r="K13" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L9" s="16" t="s">
+      <c r="L13" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M9" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N9" s="17" t="s">
+      <c r="N13" s="17" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A10" s="8">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" s="8">
         <v>46255</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B14" s="14">
         <v>420</v>
       </c>
-      <c r="C10" s="14">
+      <c r="C14" s="14">
         <v>50</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D14" s="14">
         <v>100</v>
       </c>
-      <c r="E10" s="14">
+      <c r="E14" s="14">
         <v>75</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F14" s="14">
         <v>360</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G14" s="14">
         <v>6</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H14" s="14">
         <v>80</v>
       </c>
-      <c r="I10" s="15">
+      <c r="I14" s="15">
         <f t="shared" si="0"/>
         <v>1085</v>
       </c>
-      <c r="J10" s="15">
+      <c r="J14" s="15">
         <f t="shared" si="1"/>
         <v>355</v>
       </c>
-      <c r="K10" s="16" t="s">
+      <c r="K14" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="L14" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M10" s="16" t="s">
+      <c r="M14" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N10" s="17" t="s">
+      <c r="N14" s="17" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="8">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" s="8">
         <v>46256</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B15" s="14">
         <v>540</v>
       </c>
-      <c r="C11" s="14">
+      <c r="C15" s="14">
         <v>35</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D15" s="14">
         <v>240</v>
       </c>
-      <c r="E11" s="14">
+      <c r="E15" s="14">
         <v>150</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F15" s="14">
         <v>0</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G15" s="14">
         <v>0</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H15" s="14">
         <v>120</v>
       </c>
-      <c r="I11" s="15">
+      <c r="I15" s="15">
         <f t="shared" si="0"/>
         <v>1085</v>
       </c>
-      <c r="J11" s="15">
+      <c r="J15" s="15">
         <f t="shared" si="1"/>
         <v>355</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K15" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L15" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N11" s="17" t="s">
+      <c r="N15" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A12" s="8">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="8">
         <v>46257</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B16" s="14">
         <v>510</v>
       </c>
-      <c r="C12" s="14">
+      <c r="C16" s="14">
         <v>45</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D16" s="14">
         <v>270</v>
       </c>
-      <c r="E12" s="14">
+      <c r="E16" s="14">
         <v>180</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F16" s="14">
         <v>0</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G16" s="14">
         <v>0</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H16" s="14">
         <v>90</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I16" s="15">
         <f t="shared" si="0"/>
         <v>1095</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J16" s="15">
         <f t="shared" si="1"/>
         <v>345</v>
       </c>
-      <c r="K12" s="16" t="s">
+      <c r="K16" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="16" t="s">
+      <c r="L16" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N12" s="17" t="s">
+      <c r="N16" s="17" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A13" s="8">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" s="8">
         <v>46258</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B17" s="14">
         <v>480</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C17" s="14">
         <v>40</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D17" s="14">
         <v>210</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E17" s="14">
         <v>135</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F17" s="14">
         <v>240</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G17" s="14">
         <v>4</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H17" s="14">
         <v>100</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I17" s="15">
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J17" s="15">
         <f t="shared" si="1"/>
         <v>235</v>
       </c>
-      <c r="K13" s="16" t="s">
+      <c r="K17" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="L17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="16" t="s">
+      <c r="M17" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N13" s="17" t="s">
+      <c r="N17" s="17" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A14" s="8">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" s="8">
         <v>46259</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B18" s="14">
         <v>465</v>
       </c>
-      <c r="C14" s="14">
+      <c r="C18" s="14">
         <v>35</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D18" s="14">
         <v>180</v>
       </c>
-      <c r="E14" s="14">
+      <c r="E18" s="14">
         <v>150</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F18" s="14">
         <v>300</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G18" s="14">
         <v>5</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H18" s="14">
         <v>75</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I18" s="15">
         <f t="shared" si="0"/>
         <v>1205</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J18" s="15">
         <f t="shared" si="1"/>
         <v>235</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K18" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L18" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M18" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N14" s="17" t="s">
+      <c r="N18" s="17" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A15" s="8">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" s="8">
         <v>46260</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B19" s="14">
         <v>360</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C19" s="14">
         <v>50</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D19" s="14">
         <v>210</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E19" s="14">
         <v>120</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F19" s="14">
         <v>300</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G19" s="14">
         <v>5</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H19" s="14">
         <v>60</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I19" s="15">
         <f t="shared" si="0"/>
         <v>1100</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J19" s="15">
         <f t="shared" si="1"/>
         <v>340</v>
       </c>
-      <c r="K15" s="16" t="s">
+      <c r="K19" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L15" s="16" t="s">
+      <c r="L19" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M15" s="16" t="s">
+      <c r="M19" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N15" s="17" t="s">
+      <c r="N19" s="17" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="8">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" s="8">
         <v>46261</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B20" s="14">
         <v>390</v>
       </c>
-      <c r="C16" s="14">
+      <c r="C20" s="14">
         <v>35</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D20" s="14">
         <v>180</v>
       </c>
-      <c r="E16" s="14">
+      <c r="E20" s="14">
         <v>135</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F20" s="14">
         <v>360</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H20" s="14">
         <v>75</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I20" s="15">
         <f t="shared" si="0"/>
         <v>1175</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J20" s="15">
         <f t="shared" si="1"/>
         <v>265</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K20" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="L20" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M20" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N16" s="17" t="s">
+      <c r="N20" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A17" s="8">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" s="8">
         <v>46262</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B21" s="14">
         <v>400</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C21" s="14">
         <v>40</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D21" s="14">
         <v>160</v>
       </c>
-      <c r="E17" s="14">
+      <c r="E21" s="14">
         <v>100</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F21" s="14">
         <v>240</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G21" s="14">
         <v>4</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H21" s="14">
         <v>120</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I21" s="15">
         <f t="shared" si="0"/>
         <v>1060</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J21" s="15">
         <f t="shared" si="1"/>
         <v>380</v>
       </c>
-      <c r="K17" s="16" t="s">
+      <c r="K21" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="L21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="16" t="s">
+      <c r="M21" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N17" s="17" t="s">
+      <c r="N21" s="17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A18" s="8">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" s="8">
         <v>46263</v>
       </c>
-      <c r="B18" s="14">
+      <c r="B22" s="14">
         <v>450</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C22" s="14">
         <v>30</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D22" s="14">
         <v>300</v>
       </c>
-      <c r="E18" s="14">
+      <c r="E22" s="14">
         <v>120</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F22" s="14">
         <v>0</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G22" s="14">
         <v>0</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H22" s="14">
         <v>60</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I22" s="15">
         <f t="shared" si="0"/>
         <v>960</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J22" s="15">
         <f t="shared" si="1"/>
         <v>480</v>
       </c>
-      <c r="K18" s="16" t="s">
+      <c r="K22" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="L22" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="16" t="s">
+      <c r="M22" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N18" s="17" t="s">
+      <c r="N22" s="17" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A19" s="8">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" s="8">
         <v>46264</v>
       </c>
-      <c r="B19" s="14">
+      <c r="B23" s="14">
         <v>420</v>
       </c>
-      <c r="C19" s="14">
+      <c r="C23" s="14">
         <v>55</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D23" s="14">
         <v>120</v>
       </c>
-      <c r="E19" s="14">
+      <c r="E23" s="14">
         <v>80</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F23" s="14">
         <v>0</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G23" s="14">
         <v>0</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H23" s="14">
         <v>120</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I23" s="15">
         <f t="shared" si="0"/>
         <v>795</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J23" s="15">
         <f t="shared" si="1"/>
         <v>645</v>
       </c>
-      <c r="K19" s="16" t="s">
+      <c r="K23" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="L23" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M19" s="16" t="s">
+      <c r="M23" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N19" s="17" t="s">
+      <c r="N23" s="17" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20" s="8">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="8">
         <v>46265</v>
       </c>
-      <c r="B20" s="14">
+      <c r="B24" s="14">
         <v>380</v>
       </c>
-      <c r="C20" s="14">
+      <c r="C24" s="14">
         <v>60</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D24" s="14">
         <v>300</v>
       </c>
-      <c r="E20" s="14">
+      <c r="E24" s="14">
         <v>90</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F24" s="14">
         <v>120</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G24" s="14">
         <v>2</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H24" s="14">
         <v>60</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I24" s="15">
         <f t="shared" si="0"/>
         <v>1010</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J24" s="15">
         <f t="shared" si="1"/>
         <v>430</v>
       </c>
-      <c r="K20" s="16" t="s">
+      <c r="K24" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L20" s="16" t="s">
+      <c r="L24" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="16" t="s">
+      <c r="M24" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N20" s="17" t="s">
+      <c r="N24" s="17" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21" s="8">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" s="8">
         <v>46266</v>
       </c>
-      <c r="B21" s="14">
+      <c r="B25" s="14">
         <v>420</v>
       </c>
-      <c r="C21" s="14">
+      <c r="C25" s="14">
         <v>45</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D25" s="14">
         <v>180</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E25" s="14">
         <v>60</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F25" s="14">
         <v>300</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G25" s="14">
         <v>5</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H25" s="14">
         <v>120</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I25" s="15">
         <f t="shared" si="0"/>
         <v>1125</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J25" s="15">
         <f t="shared" si="1"/>
         <v>315</v>
       </c>
-      <c r="K21" s="16" t="s">
+      <c r="K25" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="L25" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M21" s="16" t="s">
+      <c r="M25" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N21" s="17" t="s">
+      <c r="N25" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A22" s="8">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" s="8">
         <v>46267</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B26" s="14">
         <v>380</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C26" s="14">
         <v>65</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D26" s="14">
         <v>300</v>
       </c>
-      <c r="E22" s="14">
+      <c r="E26" s="14">
         <v>120</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F26" s="14">
         <v>300</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G26" s="14">
         <v>5</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H26" s="14">
         <v>45</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I26" s="15">
         <f t="shared" si="0"/>
         <v>1210</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J26" s="15">
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="K22" s="16" t="s">
+      <c r="K26" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L22" s="16" t="s">
+      <c r="L26" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M22" s="16" t="s">
+      <c r="M26" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N22" s="17" t="s">
+      <c r="N26" s="17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A23" s="8">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" s="8">
         <v>46268</v>
       </c>
-      <c r="B23" s="14">
+      <c r="B27" s="14">
         <v>400</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C27" s="14">
         <v>60</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D27" s="14">
         <v>360</v>
       </c>
-      <c r="E23" s="14">
+      <c r="E27" s="14">
         <v>60</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F27" s="14">
         <v>420</v>
       </c>
-      <c r="G23" s="14">
+      <c r="G27" s="14">
         <v>6</v>
       </c>
-      <c r="H23" s="14">
+      <c r="H27" s="14">
         <v>40</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I27" s="15">
         <f t="shared" si="0"/>
         <v>1340</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J27" s="15">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="K23" s="16" t="s">
+      <c r="K27" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L23" s="16" t="s">
+      <c r="L27" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="M23" s="16" t="s">
+      <c r="M27" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N23" s="17" t="s">
+      <c r="N27" s="17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="8">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" s="8">
         <v>46269</v>
       </c>
-      <c r="B24" s="14">
+      <c r="B28" s="14">
         <v>380</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C28" s="14">
         <v>120</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D28" s="14">
         <v>180</v>
       </c>
-      <c r="E24" s="14">
+      <c r="E28" s="14">
         <v>150</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F28" s="14">
         <v>420</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G28" s="14">
         <v>7</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H28" s="14">
         <v>60</v>
       </c>
-      <c r="I24" s="15">
+      <c r="I28" s="15">
         <f t="shared" si="0"/>
         <v>1310</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J28" s="15">
         <f t="shared" si="1"/>
         <v>130</v>
       </c>
-      <c r="K24" s="16" t="s">
+      <c r="K28" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L24" s="16" t="s">
+      <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M24" s="16" t="s">
+      <c r="M28" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N24" s="17" t="s">
+      <c r="N28" s="17" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A25" s="8">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" s="8">
         <v>46270</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B29" s="14">
         <v>420</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C29" s="14">
         <v>60</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D29" s="14">
         <v>380</v>
       </c>
-      <c r="E25" s="14">
+      <c r="E29" s="14">
         <v>190</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F29" s="14">
         <v>60</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H29" s="14">
         <v>120</v>
       </c>
-      <c r="I25" s="15">
+      <c r="I29" s="15">
         <f t="shared" si="0"/>
         <v>1230</v>
       </c>
-      <c r="J25" s="15">
+      <c r="J29" s="15">
         <f t="shared" si="1"/>
         <v>210</v>
       </c>
-      <c r="K25" s="16" t="s">
+      <c r="K29" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L25" s="16" t="s">
+      <c r="L29" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M25" s="16" t="s">
+      <c r="M29" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N25" s="17" t="s">
+      <c r="N29" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A26" s="8">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" s="8">
         <v>46271</v>
       </c>
-      <c r="B26" s="14">
+      <c r="B30" s="14">
         <v>300</v>
       </c>
-      <c r="C26" s="14">
+      <c r="C30" s="14">
         <v>120</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D30" s="14">
         <v>420</v>
       </c>
-      <c r="E26" s="14">
+      <c r="E30" s="14">
         <v>180</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F30" s="14">
         <v>0</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G30" s="14">
         <v>0</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H30" s="14">
         <v>60</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I30" s="15">
         <f t="shared" si="0"/>
         <v>1080</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J30" s="15">
         <f t="shared" si="1"/>
         <v>360</v>
       </c>
-      <c r="K26" s="16" t="s">
+      <c r="K30" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L26" s="16" t="s">
+      <c r="L30" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="16" t="s">
+      <c r="M30" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N26" s="17" t="s">
+      <c r="N30" s="17" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A27" s="8">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" s="8">
         <v>46272</v>
       </c>
-      <c r="B27" s="14">
+      <c r="B31" s="14">
         <v>320</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C31" s="14">
         <v>80</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D31" s="14">
         <v>360</v>
       </c>
-      <c r="E27" s="14">
+      <c r="E31" s="14">
         <v>120</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F31" s="14">
         <v>360</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G31" s="14">
         <v>6</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H31" s="14">
         <v>30</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I31" s="15">
         <f t="shared" si="0"/>
         <v>1270</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J31" s="15">
         <f t="shared" si="1"/>
         <v>170</v>
       </c>
-      <c r="K27" s="16" t="s">
+      <c r="K31" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="16" t="s">
+      <c r="L31" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="16" t="s">
+      <c r="M31" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N27" s="17" t="s">
+      <c r="N31" s="17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A28" s="8">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A32" s="8">
         <v>46273</v>
       </c>
-      <c r="B28" s="14">
+      <c r="B32" s="14">
         <v>380</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C32" s="14">
         <v>60</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D32" s="14">
         <v>300</v>
       </c>
-      <c r="E28" s="14">
+      <c r="E32" s="14">
         <v>60</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F32" s="14">
         <v>300</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G32" s="14">
         <v>5</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H32" s="14">
         <v>60</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I32" s="15">
         <f t="shared" si="0"/>
         <v>1160</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J32" s="15">
         <f t="shared" si="1"/>
         <v>280</v>
       </c>
-      <c r="K28" s="16" t="s">
+      <c r="K32" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L28" s="16" t="s">
+      <c r="L32" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M28" s="16" t="s">
+      <c r="M32" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N28" s="17" t="s">
+      <c r="N32" s="17" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A29" s="8">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A33" s="8">
         <v>46274</v>
       </c>
-      <c r="B29" s="14">
+      <c r="B33" s="14">
         <v>420</v>
       </c>
-      <c r="C29" s="14">
+      <c r="C33" s="14">
         <v>30</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D33" s="14">
         <v>180</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E33" s="14">
         <v>120</v>
       </c>
-      <c r="F29" s="14">
+      <c r="F33" s="14">
         <v>300</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G33" s="14">
         <v>5</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H33" s="14">
         <v>120</v>
       </c>
-      <c r="I29" s="15">
+      <c r="I33" s="15">
         <f t="shared" si="0"/>
         <v>1170</v>
       </c>
-      <c r="J29" s="15">
+      <c r="J33" s="15">
         <f t="shared" si="1"/>
         <v>270</v>
       </c>
-      <c r="K29" s="16" t="s">
+      <c r="K33" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L29" s="16" t="s">
+      <c r="L33" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M29" s="16" t="s">
+      <c r="M33" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N29" s="17" t="s">
+      <c r="N33" s="17" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A30" s="8">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A34" s="8">
         <v>46275</v>
       </c>
-      <c r="B30" s="14">
+      <c r="B34" s="14">
         <v>400</v>
       </c>
-      <c r="C30" s="14">
+      <c r="C34" s="14">
         <v>60</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D34" s="14">
         <v>60</v>
       </c>
-      <c r="E30" s="14">
+      <c r="E34" s="14">
         <v>180</v>
       </c>
-      <c r="F30" s="14">
+      <c r="F34" s="14">
         <v>120</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G34" s="14">
         <v>2</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H34" s="14">
         <v>100</v>
       </c>
-      <c r="I30" s="15">
+      <c r="I34" s="15">
         <f t="shared" si="0"/>
         <v>920</v>
       </c>
-      <c r="J30" s="15">
+      <c r="J34" s="15">
         <f t="shared" si="1"/>
         <v>520</v>
       </c>
-      <c r="K30" s="16" t="s">
+      <c r="K34" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L30" s="16" t="s">
+      <c r="L34" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="M30" s="16" t="s">
+      <c r="M34" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N30" s="17" t="s">
+      <c r="N34" s="17" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A31" s="8">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A35" s="8">
         <v>46276</v>
       </c>
-      <c r="B31" s="14">
+      <c r="B35" s="14">
         <v>380</v>
       </c>
-      <c r="C31" s="14">
+      <c r="C35" s="14">
         <v>120</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D35" s="14">
         <v>200</v>
       </c>
-      <c r="E31" s="14">
+      <c r="E35" s="14">
         <v>120</v>
       </c>
-      <c r="F31" s="14">
+      <c r="F35" s="14">
         <v>420</v>
       </c>
-      <c r="G31" s="14">
+      <c r="G35" s="14">
         <v>7</v>
       </c>
-      <c r="H31" s="14">
+      <c r="H35" s="14">
         <v>60</v>
       </c>
-      <c r="I31" s="15">
+      <c r="I35" s="15">
         <f t="shared" si="0"/>
         <v>1300</v>
       </c>
-      <c r="J31" s="15">
+      <c r="J35" s="15">
         <f t="shared" si="1"/>
         <v>140</v>
       </c>
-      <c r="K31" s="16" t="s">
+      <c r="K35" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L31" s="16" t="s">
+      <c r="L35" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M31" s="16" t="s">
+      <c r="M35" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N31" s="17" t="s">
+      <c r="N35" s="17" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A32" s="8">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A36" s="8">
         <v>46277</v>
       </c>
-      <c r="B32" s="14">
+      <c r="B36" s="14">
         <v>350</v>
       </c>
-      <c r="C32" s="14">
+      <c r="C36" s="14">
         <v>60</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D36" s="14">
         <v>450</v>
       </c>
-      <c r="E32" s="14">
+      <c r="E36" s="14">
         <v>300</v>
       </c>
-      <c r="F32" s="14">
+      <c r="F36" s="14">
         <v>0</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G36" s="14">
         <v>0</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H36" s="14">
         <v>40</v>
       </c>
-      <c r="I32" s="15">
+      <c r="I36" s="15">
         <f t="shared" si="0"/>
         <v>1200</v>
       </c>
-      <c r="J32" s="15">
+      <c r="J36" s="15">
         <f t="shared" si="1"/>
         <v>240</v>
       </c>
-      <c r="K32" s="16" t="s">
+      <c r="K36" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="L32" s="16" t="s">
+      <c r="L36" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M32" s="16" t="s">
+      <c r="M36" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="N32" s="17" t="s">
+      <c r="N36" s="17" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A33" s="8">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A37" s="8">
         <v>46278</v>
       </c>
-      <c r="B33" s="14">
+      <c r="B37" s="14">
         <v>480</v>
       </c>
-      <c r="C33" s="14">
+      <c r="C37" s="14">
         <v>75</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D37" s="14">
         <v>420</v>
       </c>
-      <c r="E33" s="14">
+      <c r="E37" s="14">
         <v>280</v>
       </c>
-      <c r="F33" s="14">
+      <c r="F37" s="14">
         <v>0</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G37" s="14">
         <v>0</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H37" s="14">
         <v>70</v>
       </c>
-      <c r="I33" s="15">
+      <c r="I37" s="15">
         <f t="shared" si="0"/>
         <v>1325</v>
       </c>
-      <c r="J33" s="15">
+      <c r="J37" s="15">
         <f t="shared" si="1"/>
         <v>115</v>
       </c>
-      <c r="K33" s="16" t="s">
+      <c r="K37" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L33" s="16" t="s">
+      <c r="L37" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M33" s="16" t="s">
+      <c r="M37" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N33" s="17" t="s">
+      <c r="N37" s="17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A34" s="8">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A38" s="8">
         <v>46279</v>
       </c>
-      <c r="B34" s="14">
+      <c r="B38" s="14">
         <v>420</v>
       </c>
-      <c r="C34" s="14">
+      <c r="C38" s="14">
         <v>45</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D38" s="14">
         <v>180</v>
       </c>
-      <c r="E34" s="14">
+      <c r="E38" s="14">
         <v>120</v>
       </c>
-      <c r="F34" s="14">
+      <c r="F38" s="14">
         <v>240</v>
       </c>
-      <c r="G34" s="14">
+      <c r="G38" s="14">
         <v>4</v>
       </c>
-      <c r="H34" s="14">
+      <c r="H38" s="14">
         <v>180</v>
       </c>
-      <c r="I34" s="15">
+      <c r="I38" s="15">
         <f t="shared" si="0"/>
         <v>1185</v>
       </c>
-      <c r="J34" s="15">
+      <c r="J38" s="15">
         <f t="shared" si="1"/>
         <v>255</v>
       </c>
-      <c r="K34" s="16" t="s">
+      <c r="K38" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="L34" s="16" t="s">
+      <c r="L38" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="M34" s="16" t="s">
+      <c r="M38" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="N34" s="17" t="s">
+      <c r="N38" s="17" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A35" s="8">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A39" s="8">
         <v>46280</v>
       </c>
-      <c r="B35" s="14">
+      <c r="B39" s="14">
         <v>400</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C39" s="14">
         <v>90</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D39" s="14">
         <v>120</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E39" s="14">
         <v>180</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F39" s="14">
         <v>300</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G39" s="14">
         <v>5</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H39" s="14">
         <v>120</v>
       </c>
-      <c r="I35" s="15">
+      <c r="I39" s="15">
         <f t="shared" si="0"/>
         <v>1210</v>
       </c>
-      <c r="J35" s="15">
+      <c r="J39" s="15">
         <f t="shared" si="1"/>
         <v>230</v>
       </c>
-      <c r="K35" s="16" t="s">
+      <c r="K39" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L35" s="16" t="s">
+      <c r="L39" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="M35" s="16" t="s">
+      <c r="M39" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N35" s="17" t="s">
+      <c r="N39" s="17" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A36" s="8">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A40" s="8">
         <v>46281</v>
       </c>
-      <c r="B36" s="14">
+      <c r="B40" s="14">
         <v>390</v>
       </c>
-      <c r="C36" s="14">
+      <c r="C40" s="14">
         <v>45</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D40" s="14">
         <v>180</v>
       </c>
-      <c r="E36" s="14">
+      <c r="E40" s="14">
         <v>60</v>
       </c>
-      <c r="F36" s="14">
+      <c r="F40" s="14">
         <v>180</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G40" s="14">
         <v>3</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H40" s="14">
         <v>210</v>
       </c>
-      <c r="I36" s="15">
+      <c r="I40" s="15">
         <f t="shared" si="0"/>
         <v>1065</v>
       </c>
-      <c r="J36" s="15">
+      <c r="J40" s="15">
         <f t="shared" si="1"/>
         <v>375</v>
       </c>
-      <c r="K36" s="16" t="s">
+      <c r="K40" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="L36" s="16" t="s">
+      <c r="L40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M36" s="16" t="s">
+      <c r="M40" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="N36" s="17" t="s">
+      <c r="N40" s="17" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A37" s="13"/>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15" t="str">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A41" s="8">
+        <v>46282</v>
+      </c>
+      <c r="B41" s="14">
+        <v>320</v>
+      </c>
+      <c r="C41" s="14">
+        <v>60</v>
+      </c>
+      <c r="D41" s="14">
+        <v>220</v>
+      </c>
+      <c r="E41" s="14">
+        <v>120</v>
+      </c>
+      <c r="F41" s="14">
+        <v>360</v>
+      </c>
+      <c r="G41" s="14">
+        <v>6</v>
+      </c>
+      <c r="H41" s="14">
+        <v>60</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J37" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K37" s="16"/>
-      <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="17"/>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A38" s="13"/>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J38" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="17"/>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A39" s="13"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J39" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="17"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A40" s="13"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J40" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="17"/>
-    </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>
@@ -3244,11 +3368,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3266,11 +3390,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3288,11 +3412,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3310,11 +3434,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3332,11 +3456,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I74:I137" si="2">IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J74:J137" si="3">IF(I74="","",1440-I74)</f>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -4652,11 +4776,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4674,11 +4798,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4696,11 +4820,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4718,11 +4842,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4740,11 +4864,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I138:I201" si="4">IF(SUM(B138:F138,H138)=0,"",SUM(B138:F138,H138))</f>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J138:J201" si="5">IF(I138="","",1440-I138)</f>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -6060,11 +6184,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6082,11 +6206,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6104,11 +6228,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6126,11 +6250,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6148,11 +6272,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I202:I265" si="6">IF(SUM(B202:F202,H202)=0,"",SUM(B202:F202,H202))</f>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J202:J265" si="7">IF(I202="","",1440-I202)</f>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -7468,11 +7592,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7490,11 +7614,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7512,11 +7636,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7534,11 +7658,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7556,11 +7680,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I266:I329" si="8">IF(SUM(B266:F266,H266)=0,"",SUM(B266:F266,H266))</f>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J266:J329" si="9">IF(I266="","",1440-I266)</f>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -8876,11 +9000,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -8898,11 +9022,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -8920,11 +9044,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -8942,11 +9066,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -8964,11 +9088,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I330:I393" si="10">IF(SUM(B330:F330,H330)=0,"",SUM(B330:F330,H330))</f>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J330:J393" si="11">IF(I330="","",1440-I330)</f>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -10284,11 +10408,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10306,11 +10430,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10328,11 +10452,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10350,11 +10474,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10372,11 +10496,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="I394:I405" si="12">IF(SUM(B394:F394,H394)=0,"",SUM(B394:F394,H394))</f>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="J394:J405" si="13">IF(I394="","",1440-I394)</f>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10538,6 +10662,94 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
+    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A402" s="13"/>
+      <c r="B402" s="14"/>
+      <c r="C402" s="14"/>
+      <c r="D402" s="14"/>
+      <c r="E402" s="14"/>
+      <c r="F402" s="14"/>
+      <c r="G402" s="14"/>
+      <c r="H402" s="14"/>
+      <c r="I402" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J402" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K402" s="16"/>
+      <c r="L402" s="16"/>
+      <c r="M402" s="16"/>
+      <c r="N402" s="17"/>
+    </row>
+    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A403" s="13"/>
+      <c r="B403" s="14"/>
+      <c r="C403" s="14"/>
+      <c r="D403" s="14"/>
+      <c r="E403" s="14"/>
+      <c r="F403" s="14"/>
+      <c r="G403" s="14"/>
+      <c r="H403" s="14"/>
+      <c r="I403" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J403" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K403" s="16"/>
+      <c r="L403" s="16"/>
+      <c r="M403" s="16"/>
+      <c r="N403" s="17"/>
+    </row>
+    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A404" s="13"/>
+      <c r="B404" s="14"/>
+      <c r="C404" s="14"/>
+      <c r="D404" s="14"/>
+      <c r="E404" s="14"/>
+      <c r="F404" s="14"/>
+      <c r="G404" s="14"/>
+      <c r="H404" s="14"/>
+      <c r="I404" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J404" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K404" s="16"/>
+      <c r="L404" s="16"/>
+      <c r="M404" s="16"/>
+      <c r="N404" s="17"/>
+    </row>
+    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A405" s="13"/>
+      <c r="B405" s="14"/>
+      <c r="C405" s="14"/>
+      <c r="D405" s="14"/>
+      <c r="E405" s="14"/>
+      <c r="F405" s="14"/>
+      <c r="G405" s="14"/>
+      <c r="H405" s="14"/>
+      <c r="I405" s="15" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="J405" s="15" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="K405" s="16"/>
+      <c r="L405" s="16"/>
+      <c r="M405" s="16"/>
+      <c r="N405" s="17"/>
+    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10547,21 +10759,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
+  <conditionalFormatting sqref="J6:J405">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K405" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L405" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M405" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F66C4296-03EB-4D50-BC12-804B7F491C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C9679-F11E-4F17-938B-58777BA88FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -310,6 +310,9 @@
   </si>
   <si>
     <t>hectic day.</t>
+  </si>
+  <si>
+    <t>feeling exhausted.</t>
   </si>
 </sst>
 </file>
@@ -2743,26 +2746,50 @@
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+      <c r="A42" s="8">
+        <v>46283</v>
+      </c>
+      <c r="B42" s="14">
+        <v>300</v>
+      </c>
+      <c r="C42" s="14">
+        <v>30</v>
+      </c>
+      <c r="D42" s="14">
+        <v>220</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>420</v>
+      </c>
+      <c r="G42" s="14">
+        <v>7</v>
+      </c>
+      <c r="H42" s="14">
+        <v>30</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C04C9679-F11E-4F17-938B-58777BA88FA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6123A9-2460-458B-BE0F-9349694426F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="93">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -313,6 +313,9 @@
   </si>
   <si>
     <t>feeling exhausted.</t>
+  </si>
+  <si>
+    <t>health issues.</t>
   </si>
 </sst>
 </file>
@@ -2792,26 +2795,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="8">
+        <v>46284</v>
+      </c>
+      <c r="B43" s="14">
+        <v>340</v>
+      </c>
+      <c r="C43" s="14">
+        <v>60</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>90</v>
+      </c>
+      <c r="F43" s="14">
+        <v>0</v>
+      </c>
+      <c r="G43" s="14">
+        <v>0</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C6123A9-2460-458B-BE0F-9349694426F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DC7960-54AF-48C8-B932-D894E4515A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="96">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -316,6 +316,15 @@
   </si>
   <si>
     <t>health issues.</t>
+  </si>
+  <si>
+    <t>Stressed</t>
+  </si>
+  <si>
+    <t>Very Unsatisfied</t>
+  </si>
+  <si>
+    <t>high fever.</t>
   </si>
 </sst>
 </file>
@@ -2841,26 +2850,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="8">
+        <v>46285</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>20</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>180</v>
+      </c>
+      <c r="F44" s="14">
+        <v>0</v>
+      </c>
+      <c r="G44" s="14">
+        <v>0</v>
+      </c>
+      <c r="H44" s="14">
+        <v>30</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>770</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>670</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70DC7960-54AF-48C8-B932-D894E4515A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A4E934-3A7E-4C8A-B3B9-D2DFC9D50DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>high fever.</t>
+  </si>
+  <si>
+    <t>relaxing day.</t>
   </si>
 </sst>
 </file>
@@ -2896,26 +2899,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="8">
+        <v>46286</v>
+      </c>
+      <c r="B45" s="14">
+        <v>420</v>
+      </c>
+      <c r="C45" s="14">
+        <v>30</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>90</v>
+      </c>
+      <c r="F45" s="14">
+        <v>240</v>
+      </c>
+      <c r="G45" s="14">
+        <v>4</v>
+      </c>
+      <c r="H45" s="14">
+        <v>60</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2A4E934-3A7E-4C8A-B3B9-D2DFC9D50DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A3F99A-A21A-4B16-9115-20A5B206E924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -309,9 +309,6 @@
     <t>good day.</t>
   </si>
   <si>
-    <t>hectic day.</t>
-  </si>
-  <si>
     <t>feeling exhausted.</t>
   </si>
   <si>
@@ -328,6 +325,9 @@
   </si>
   <si>
     <t>relaxing day.</t>
+  </si>
+  <si>
+    <t>fever.</t>
   </si>
 </sst>
 </file>
@@ -978,7 +978,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N405"/>
+  <dimension ref="A1:N401"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1108,7 +1108,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B6" s="9">
         <v>420</v>
@@ -1123,21 +1123,19 @@
         <v>90</v>
       </c>
       <c r="F6" s="9">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G6" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H6" s="9">
         <v>60</v>
       </c>
       <c r="I6" s="10">
-        <f t="shared" ref="I6:I73" si="0">IF(SUM(B6:F6,H6)=0,"",SUM(B6:F6,H6))</f>
-        <v>1095</v>
+        <v>795</v>
       </c>
       <c r="J6" s="10">
-        <f t="shared" ref="J6:J73" si="1">IF(I6="","",1440-I6)</f>
-        <v>345</v>
+        <v>645</v>
       </c>
       <c r="K6" s="11" t="s">
         <v>49</v>
@@ -1154,221 +1152,223 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
-        <v>46248</v>
-      </c>
-      <c r="B7" s="9">
-        <v>380</v>
-      </c>
-      <c r="C7" s="9">
-        <v>35</v>
-      </c>
-      <c r="D7" s="9">
+        <v>46252</v>
+      </c>
+      <c r="B7" s="14">
+        <v>450</v>
+      </c>
+      <c r="C7" s="14">
+        <v>30</v>
+      </c>
+      <c r="D7" s="14">
+        <v>150</v>
+      </c>
+      <c r="E7" s="14">
         <v>120</v>
       </c>
-      <c r="E7" s="9">
-        <v>60</v>
-      </c>
-      <c r="F7" s="9">
-        <v>300</v>
-      </c>
-      <c r="G7" s="9">
-        <v>5</v>
-      </c>
-      <c r="H7" s="9">
-        <v>120</v>
-      </c>
-      <c r="I7" s="10">
-        <f t="shared" si="0"/>
-        <v>1015</v>
-      </c>
-      <c r="J7" s="10">
-        <f t="shared" si="1"/>
-        <v>425</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="L7" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N7" s="12" t="s">
-        <v>89</v>
+      <c r="F7" s="14">
+        <v>420</v>
+      </c>
+      <c r="G7" s="14">
+        <v>6</v>
+      </c>
+      <c r="H7" s="14">
+        <v>45</v>
+      </c>
+      <c r="I7" s="15">
+        <f t="shared" ref="I7:I69" si="0">IF(SUM(B7:F7,H7)=0,"",SUM(B7:F7,H7))</f>
+        <v>1215</v>
+      </c>
+      <c r="J7" s="15">
+        <f t="shared" ref="J7:J69" si="1">IF(I7="","",1440-I7)</f>
+        <v>225</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
-        <v>46249</v>
-      </c>
-      <c r="B8" s="9">
-        <v>400</v>
-      </c>
-      <c r="C8" s="9">
+        <v>46253</v>
+      </c>
+      <c r="B8" s="14">
+        <v>480</v>
+      </c>
+      <c r="C8" s="14">
+        <v>40</v>
+      </c>
+      <c r="D8" s="14">
+        <v>120</v>
+      </c>
+      <c r="E8" s="14">
+        <v>100</v>
+      </c>
+      <c r="F8" s="14">
+        <v>420</v>
+      </c>
+      <c r="G8" s="14">
+        <v>7</v>
+      </c>
+      <c r="H8" s="14">
+        <v>30</v>
+      </c>
+      <c r="I8" s="15">
+        <f t="shared" si="0"/>
+        <v>1190</v>
+      </c>
+      <c r="J8" s="15">
+        <f t="shared" si="1"/>
+        <v>250</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>60</v>
-      </c>
-      <c r="D8" s="9">
-        <v>210</v>
-      </c>
-      <c r="E8" s="9">
-        <v>45</v>
-      </c>
-      <c r="F8" s="9">
-        <v>360</v>
-      </c>
-      <c r="G8" s="9">
-        <v>6</v>
-      </c>
-      <c r="H8" s="9">
-        <v>30</v>
-      </c>
-      <c r="I8" s="10">
-        <f t="shared" si="0"/>
-        <v>1105</v>
-      </c>
-      <c r="J8" s="10">
-        <f t="shared" si="1"/>
-        <v>335</v>
-      </c>
-      <c r="K8" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="L8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8" s="12" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="8">
-        <v>46250</v>
-      </c>
-      <c r="B9" s="9">
-        <v>380</v>
-      </c>
-      <c r="C9" s="9">
+        <v>46254</v>
+      </c>
+      <c r="B9" s="14">
+        <v>450</v>
+      </c>
+      <c r="C9" s="14">
+        <v>30</v>
+      </c>
+      <c r="D9" s="14">
+        <v>150</v>
+      </c>
+      <c r="E9" s="14">
+        <v>120</v>
+      </c>
+      <c r="F9" s="14">
+        <v>240</v>
+      </c>
+      <c r="G9" s="14">
+        <v>4</v>
+      </c>
+      <c r="H9" s="14">
         <v>45</v>
       </c>
-      <c r="D9" s="9">
-        <v>180</v>
-      </c>
-      <c r="E9" s="9">
-        <v>35</v>
-      </c>
-      <c r="F9" s="9">
-        <v>420</v>
-      </c>
-      <c r="G9" s="9">
-        <v>7</v>
-      </c>
-      <c r="H9" s="9">
-        <v>60</v>
-      </c>
-      <c r="I9" s="10">
+      <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
-      </c>
-      <c r="J9" s="10">
+        <v>1035</v>
+      </c>
+      <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="N9" s="12" t="s">
-        <v>90</v>
+        <v>405</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N9" s="17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A10" s="8">
-        <v>46251</v>
-      </c>
-      <c r="B10" s="9">
+        <v>46255</v>
+      </c>
+      <c r="B10" s="14">
         <v>420</v>
       </c>
-      <c r="C10" s="9">
-        <v>45</v>
-      </c>
-      <c r="D10" s="9">
-        <v>180</v>
-      </c>
-      <c r="E10" s="9">
-        <v>90</v>
-      </c>
-      <c r="F10" s="9">
-        <v>0</v>
-      </c>
-      <c r="G10" s="9">
-        <v>0</v>
-      </c>
-      <c r="H10" s="9">
-        <v>60</v>
-      </c>
-      <c r="I10" s="10">
-        <v>795</v>
-      </c>
-      <c r="J10" s="10">
-        <v>645</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="11" t="s">
+      <c r="C10" s="14">
         <v>50</v>
       </c>
-      <c r="M10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="N10" s="12" t="s">
-        <v>58</v>
+      <c r="D10" s="14">
+        <v>100</v>
+      </c>
+      <c r="E10" s="14">
+        <v>75</v>
+      </c>
+      <c r="F10" s="14">
+        <v>360</v>
+      </c>
+      <c r="G10" s="14">
+        <v>6</v>
+      </c>
+      <c r="H10" s="14">
+        <v>80</v>
+      </c>
+      <c r="I10" s="15">
+        <f t="shared" si="0"/>
+        <v>1085</v>
+      </c>
+      <c r="J10" s="15">
+        <f t="shared" si="1"/>
+        <v>355</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L10" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="8">
-        <v>46252</v>
+        <v>46256</v>
       </c>
       <c r="B11" s="14">
-        <v>450</v>
+        <v>540</v>
       </c>
       <c r="C11" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D11" s="14">
+        <v>240</v>
+      </c>
+      <c r="E11" s="14">
         <v>150</v>
       </c>
-      <c r="E11" s="14">
+      <c r="F11" s="14">
+        <v>0</v>
+      </c>
+      <c r="G11" s="14">
+        <v>0</v>
+      </c>
+      <c r="H11" s="14">
         <v>120</v>
-      </c>
-      <c r="F11" s="14">
-        <v>420</v>
-      </c>
-      <c r="G11" s="14">
-        <v>6</v>
-      </c>
-      <c r="H11" s="14">
-        <v>45</v>
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>1215</v>
+        <v>1085</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>225</v>
+        <v>355</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L11" s="16" t="s">
         <v>50</v>
@@ -1377,70 +1377,70 @@
         <v>51</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" s="8">
-        <v>46253</v>
+        <v>46257</v>
       </c>
       <c r="B12" s="14">
-        <v>480</v>
+        <v>510</v>
       </c>
       <c r="C12" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D12" s="14">
-        <v>120</v>
+        <v>270</v>
       </c>
       <c r="E12" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="F12" s="14">
-        <v>420</v>
+        <v>0</v>
       </c>
       <c r="G12" s="14">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H12" s="14">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1190</v>
+        <v>1095</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>250</v>
+        <v>345</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L12" s="16" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="M12" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" s="8">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B13" s="14">
-        <v>450</v>
+        <v>480</v>
       </c>
       <c r="C13" s="14">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D13" s="14">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="E13" s="14">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="F13" s="14">
         <v>240</v>
@@ -1449,64 +1449,64 @@
         <v>4</v>
       </c>
       <c r="H13" s="14">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>1035</v>
+        <v>1205</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>405</v>
+        <v>235</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>55</v>
       </c>
       <c r="L13" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M13" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" s="8">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B14" s="14">
-        <v>420</v>
+        <v>465</v>
       </c>
       <c r="C14" s="14">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="D14" s="14">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="E14" s="14">
+        <v>150</v>
+      </c>
+      <c r="F14" s="14">
+        <v>300</v>
+      </c>
+      <c r="G14" s="14">
+        <v>5</v>
+      </c>
+      <c r="H14" s="14">
         <v>75</v>
-      </c>
-      <c r="F14" s="14">
-        <v>360</v>
-      </c>
-      <c r="G14" s="14">
-        <v>6</v>
-      </c>
-      <c r="H14" s="14">
-        <v>80</v>
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>1085</v>
+        <v>1205</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>355</v>
+        <v>235</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>54</v>
@@ -1515,116 +1515,116 @@
         <v>64</v>
       </c>
       <c r="N14" s="17" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" s="8">
-        <v>46256</v>
+        <v>46260</v>
       </c>
       <c r="B15" s="14">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="C15" s="14">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D15" s="14">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="E15" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F15" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G15" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H15" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="I15" s="15">
         <f t="shared" si="0"/>
-        <v>1085</v>
+        <v>1100</v>
       </c>
       <c r="J15" s="15">
         <f t="shared" si="1"/>
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M15" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="8">
-        <v>46257</v>
+        <v>46261</v>
       </c>
       <c r="B16" s="14">
-        <v>510</v>
+        <v>390</v>
       </c>
       <c r="C16" s="14">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D16" s="14">
-        <v>270</v>
+        <v>180</v>
       </c>
       <c r="E16" s="14">
-        <v>180</v>
+        <v>135</v>
       </c>
       <c r="F16" s="14">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G16" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H16" s="14">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>1095</v>
+        <v>1175</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>345</v>
+        <v>265</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L16" s="16" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="M16" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" s="8">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="B17" s="14">
-        <v>480</v>
+        <v>400</v>
       </c>
       <c r="C17" s="14">
         <v>40</v>
       </c>
       <c r="D17" s="14">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="E17" s="14">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
         <v>240</v>
@@ -1633,110 +1633,110 @@
         <v>4</v>
       </c>
       <c r="H17" s="14">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>1205</v>
+        <v>1060</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>235</v>
+        <v>380</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L17" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M17" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" s="8">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="B18" s="14">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="C18" s="14">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D18" s="14">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E18" s="14">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="F18" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18" s="14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>1205</v>
+        <v>960</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>235</v>
+        <v>480</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="L18" s="16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M18" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
-        <v>46260</v>
+        <v>46264</v>
       </c>
       <c r="B19" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="C19" s="14">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D19" s="14">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="E19" s="14">
+        <v>80</v>
+      </c>
+      <c r="F19" s="14">
+        <v>0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>0</v>
+      </c>
+      <c r="H19" s="14">
         <v>120</v>
-      </c>
-      <c r="F19" s="14">
-        <v>300</v>
-      </c>
-      <c r="G19" s="14">
-        <v>5</v>
-      </c>
-      <c r="H19" s="14">
-        <v>60</v>
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>1100</v>
+        <v>795</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>340</v>
+        <v>645</v>
       </c>
       <c r="K19" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L19" s="16" t="s">
         <v>54</v>
@@ -1745,50 +1745,50 @@
         <v>51</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B20" s="14">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="C20" s="14">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D20" s="14">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E20" s="14">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="F20" s="14">
-        <v>360</v>
+        <v>120</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H20" s="14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>1175</v>
+        <v>1010</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>265</v>
+        <v>430</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L20" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N20" s="17" t="s">
         <v>72</v>
@@ -1796,59 +1796,59 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B21" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C21" s="14">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D21" s="14">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="E21" s="14">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="F21" s="14">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="G21" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H21" s="14">
         <v>120</v>
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1125</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>315</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L21" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M21" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N21" s="17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
-        <v>46263</v>
+        <v>46267</v>
       </c>
       <c r="B22" s="14">
-        <v>450</v>
+        <v>380</v>
       </c>
       <c r="C22" s="14">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D22" s="14">
         <v>300</v>
@@ -1857,24 +1857,24 @@
         <v>120</v>
       </c>
       <c r="F22" s="14">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G22" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H22" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1210</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>230</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="L22" s="16" t="s">
         <v>50</v>
@@ -1883,87 +1883,87 @@
         <v>51</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" s="8">
-        <v>46264</v>
+        <v>46268</v>
       </c>
       <c r="B23" s="14">
+        <v>400</v>
+      </c>
+      <c r="C23" s="14">
+        <v>60</v>
+      </c>
+      <c r="D23" s="14">
+        <v>360</v>
+      </c>
+      <c r="E23" s="14">
+        <v>60</v>
+      </c>
+      <c r="F23" s="14">
         <v>420</v>
       </c>
-      <c r="C23" s="14">
-        <v>55</v>
-      </c>
-      <c r="D23" s="14">
-        <v>120</v>
-      </c>
-      <c r="E23" s="14">
-        <v>80</v>
-      </c>
-      <c r="F23" s="14">
-        <v>0</v>
-      </c>
       <c r="G23" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H23" s="14">
-        <v>120</v>
+        <v>40</v>
       </c>
       <c r="I23" s="15">
         <f t="shared" si="0"/>
-        <v>795</v>
+        <v>1340</v>
       </c>
       <c r="J23" s="15">
         <f t="shared" si="1"/>
-        <v>645</v>
+        <v>100</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="M23" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" s="8">
-        <v>46265</v>
+        <v>46269</v>
       </c>
       <c r="B24" s="14">
         <v>380</v>
       </c>
       <c r="C24" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="D24" s="14">
-        <v>300</v>
+        <v>180</v>
       </c>
       <c r="E24" s="14">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="F24" s="14">
-        <v>120</v>
+        <v>420</v>
       </c>
       <c r="G24" s="14">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H24" s="14">
         <v>60</v>
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1310</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>130</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>55</v>
@@ -1975,225 +1975,225 @@
         <v>57</v>
       </c>
       <c r="N24" s="17" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" s="8">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="B25" s="14">
         <v>420</v>
       </c>
       <c r="C25" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D25" s="14">
-        <v>180</v>
+        <v>380</v>
       </c>
       <c r="E25" s="14">
+        <v>190</v>
+      </c>
+      <c r="F25" s="14">
         <v>60</v>
       </c>
-      <c r="F25" s="14">
-        <v>300</v>
-      </c>
       <c r="G25" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H25" s="14">
         <v>120</v>
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>1125</v>
+        <v>1230</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>315</v>
+        <v>210</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M25" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" s="8">
-        <v>46267</v>
+        <v>46271</v>
       </c>
       <c r="B26" s="14">
-        <v>380</v>
+        <v>300</v>
       </c>
       <c r="C26" s="14">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D26" s="14">
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="E26" s="14">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="F26" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G26" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H26" s="14">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>1080</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>360</v>
       </c>
       <c r="K26" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L26" s="16" t="s">
         <v>54</v>
-      </c>
-      <c r="L26" s="16" t="s">
-        <v>50</v>
       </c>
       <c r="M26" s="16" t="s">
         <v>51</v>
       </c>
       <c r="N26" s="17" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" s="8">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="B27" s="14">
-        <v>400</v>
+        <v>320</v>
       </c>
       <c r="C27" s="14">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D27" s="14">
         <v>360</v>
       </c>
       <c r="E27" s="14">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="F27" s="14">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="G27" s="14">
         <v>6</v>
       </c>
       <c r="H27" s="14">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>1340</v>
+        <v>1270</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="L27" s="16" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="M27" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N27" s="17" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" s="8">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B28" s="14">
         <v>380</v>
       </c>
       <c r="C28" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D28" s="14">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="E28" s="14">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F28" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="14">
         <v>60</v>
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>1310</v>
+        <v>1160</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L28" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" s="8">
-        <v>46270</v>
+        <v>46274</v>
       </c>
       <c r="B29" s="14">
         <v>420</v>
       </c>
       <c r="C29" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D29" s="14">
-        <v>380</v>
+        <v>180</v>
       </c>
       <c r="E29" s="14">
-        <v>190</v>
+        <v>120</v>
       </c>
       <c r="F29" s="14">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H29" s="14">
         <v>120</v>
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>1230</v>
+        <v>1170</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>210</v>
+        <v>270</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
@@ -2205,179 +2205,179 @@
         <v>51</v>
       </c>
       <c r="N29" s="17" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" s="8">
-        <v>46271</v>
+        <v>46275</v>
       </c>
       <c r="B30" s="14">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C30" s="14">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="D30" s="14">
-        <v>420</v>
+        <v>60</v>
       </c>
       <c r="E30" s="14">
         <v>180</v>
       </c>
       <c r="F30" s="14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="G30" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H30" s="14">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>920</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>520</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="8">
-        <v>46272</v>
+        <v>46276</v>
       </c>
       <c r="B31" s="14">
-        <v>320</v>
+        <v>380</v>
       </c>
       <c r="C31" s="14">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="D31" s="14">
-        <v>360</v>
+        <v>200</v>
       </c>
       <c r="E31" s="14">
         <v>120</v>
       </c>
       <c r="F31" s="14">
-        <v>360</v>
+        <v>420</v>
       </c>
       <c r="G31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H31" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>1270</v>
+        <v>1300</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L31" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M31" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A32" s="8">
-        <v>46273</v>
+        <v>46277</v>
       </c>
       <c r="B32" s="14">
-        <v>380</v>
+        <v>350</v>
       </c>
       <c r="C32" s="14">
         <v>60</v>
       </c>
       <c r="D32" s="14">
+        <v>450</v>
+      </c>
+      <c r="E32" s="14">
         <v>300</v>
       </c>
-      <c r="E32" s="14">
-        <v>60</v>
-      </c>
       <c r="F32" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G32" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H32" s="14">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1160</v>
+        <v>1200</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L32" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A33" s="8">
-        <v>46274</v>
+        <v>46278</v>
       </c>
       <c r="B33" s="14">
+        <v>480</v>
+      </c>
+      <c r="C33" s="14">
+        <v>75</v>
+      </c>
+      <c r="D33" s="14">
         <v>420</v>
       </c>
-      <c r="C33" s="14">
-        <v>30</v>
-      </c>
-      <c r="D33" s="14">
-        <v>180</v>
-      </c>
       <c r="E33" s="14">
-        <v>120</v>
+        <v>280</v>
       </c>
       <c r="F33" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G33" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H33" s="14">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>1170</v>
+        <v>1325</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>270</v>
+        <v>115</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>49</v>
@@ -2389,87 +2389,87 @@
         <v>51</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A34" s="8">
-        <v>46275</v>
+        <v>46279</v>
       </c>
       <c r="B34" s="14">
-        <v>400</v>
+        <v>420</v>
       </c>
       <c r="C34" s="14">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="D34" s="14">
-        <v>60</v>
+        <v>180</v>
       </c>
       <c r="E34" s="14">
+        <v>120</v>
+      </c>
+      <c r="F34" s="14">
+        <v>240</v>
+      </c>
+      <c r="G34" s="14">
+        <v>4</v>
+      </c>
+      <c r="H34" s="14">
         <v>180</v>
-      </c>
-      <c r="F34" s="14">
-        <v>120</v>
-      </c>
-      <c r="G34" s="14">
-        <v>2</v>
-      </c>
-      <c r="H34" s="14">
-        <v>100</v>
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>920</v>
+        <v>1185</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>520</v>
+        <v>255</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L34" s="16" t="s">
         <v>67</v>
       </c>
       <c r="M34" s="16" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="N34" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A35" s="8">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="B35" s="14">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="C35" s="14">
+        <v>90</v>
+      </c>
+      <c r="D35" s="14">
         <v>120</v>
       </c>
-      <c r="D35" s="14">
-        <v>200</v>
-      </c>
       <c r="E35" s="14">
+        <v>180</v>
+      </c>
+      <c r="F35" s="14">
+        <v>300</v>
+      </c>
+      <c r="G35" s="14">
+        <v>5</v>
+      </c>
+      <c r="H35" s="14">
         <v>120</v>
-      </c>
-      <c r="F35" s="14">
-        <v>420</v>
-      </c>
-      <c r="G35" s="14">
-        <v>7</v>
-      </c>
-      <c r="H35" s="14">
-        <v>60</v>
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1300</v>
+        <v>1210</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>49</v>
@@ -2481,468 +2481,396 @@
         <v>51</v>
       </c>
       <c r="N35" s="17" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A36" s="8">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="B36" s="14">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="C36" s="14">
+        <v>45</v>
+      </c>
+      <c r="D36" s="14">
+        <v>180</v>
+      </c>
+      <c r="E36" s="14">
         <v>60</v>
       </c>
-      <c r="D36" s="14">
-        <v>450</v>
-      </c>
-      <c r="E36" s="14">
-        <v>300</v>
-      </c>
       <c r="F36" s="14">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G36" s="14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H36" s="14">
-        <v>40</v>
+        <v>210</v>
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1200</v>
+        <v>1065</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>240</v>
+        <v>375</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L36" s="16" t="s">
         <v>50</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A37" s="8">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="B37" s="14">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="C37" s="14">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="D37" s="14">
-        <v>420</v>
+        <v>220</v>
       </c>
       <c r="E37" s="14">
-        <v>280</v>
+        <v>120</v>
       </c>
       <c r="F37" s="14">
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="G37" s="14">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H37" s="14">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1325</v>
+        <v>1140</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>115</v>
+        <v>300</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A38" s="8">
-        <v>46279</v>
+        <v>46283</v>
       </c>
       <c r="B38" s="14">
+        <v>300</v>
+      </c>
+      <c r="C38" s="14">
+        <v>30</v>
+      </c>
+      <c r="D38" s="14">
+        <v>220</v>
+      </c>
+      <c r="E38" s="14">
+        <v>60</v>
+      </c>
+      <c r="F38" s="14">
         <v>420</v>
       </c>
-      <c r="C38" s="14">
-        <v>45</v>
-      </c>
-      <c r="D38" s="14">
-        <v>180</v>
-      </c>
-      <c r="E38" s="14">
-        <v>120</v>
-      </c>
-      <c r="F38" s="14">
-        <v>240</v>
-      </c>
       <c r="G38" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H38" s="14">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>1185</v>
+        <v>1060</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>255</v>
+        <v>380</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A39" s="8">
-        <v>46280</v>
+        <v>46284</v>
       </c>
       <c r="B39" s="14">
-        <v>400</v>
+        <v>340</v>
       </c>
       <c r="C39" s="14">
+        <v>60</v>
+      </c>
+      <c r="D39" s="14">
+        <v>180</v>
+      </c>
+      <c r="E39" s="14">
         <v>90</v>
       </c>
-      <c r="D39" s="14">
-        <v>120</v>
-      </c>
-      <c r="E39" s="14">
-        <v>180</v>
-      </c>
       <c r="F39" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G39" s="14">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H39" s="14">
         <v>120</v>
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>1210</v>
+        <v>790</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>230</v>
+        <v>650</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A40" s="8">
-        <v>46281</v>
+        <v>46285</v>
       </c>
       <c r="B40" s="14">
-        <v>390</v>
+        <v>420</v>
       </c>
       <c r="C40" s="14">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D40" s="14">
+        <v>120</v>
+      </c>
+      <c r="E40" s="14">
         <v>180</v>
       </c>
-      <c r="E40" s="14">
-        <v>60</v>
-      </c>
       <c r="F40" s="14">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G40" s="14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H40" s="14">
-        <v>210</v>
+        <v>30</v>
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>1065</v>
+        <v>770</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>375</v>
+        <v>670</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>54</v>
+        <v>92</v>
       </c>
       <c r="L40" s="16" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N40" s="17" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A41" s="8">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="B41" s="14">
-        <v>320</v>
+        <v>420</v>
       </c>
       <c r="C41" s="14">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D41" s="14">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="E41" s="14">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="F41" s="14">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="G41" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H41" s="14">
         <v>60</v>
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>1140</v>
+        <v>1020</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>300</v>
+        <v>420</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>49</v>
       </c>
       <c r="L41" s="16" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="M41" s="16" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="N41" s="17" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="8">
-        <v>46283</v>
+        <v>46287</v>
       </c>
       <c r="B42" s="14">
-        <v>300</v>
+        <v>380</v>
       </c>
       <c r="C42" s="14">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="D42" s="14">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="E42" s="14">
         <v>60</v>
       </c>
       <c r="F42" s="14">
-        <v>420</v>
+        <v>300</v>
       </c>
       <c r="G42" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H42" s="14">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1040</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="8">
-        <v>46284</v>
-      </c>
-      <c r="B43" s="14">
-        <v>340</v>
-      </c>
-      <c r="C43" s="14">
-        <v>60</v>
-      </c>
-      <c r="D43" s="14">
-        <v>180</v>
-      </c>
-      <c r="E43" s="14">
-        <v>90</v>
-      </c>
-      <c r="F43" s="14">
-        <v>0</v>
-      </c>
-      <c r="G43" s="14">
-        <v>0</v>
-      </c>
-      <c r="H43" s="14">
-        <v>120</v>
-      </c>
-      <c r="I43" s="15">
+      <c r="A43" s="13"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>790</v>
-      </c>
-      <c r="J43" s="15">
+        <v/>
+      </c>
+      <c r="J43" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>650</v>
-      </c>
-      <c r="K43" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="L43" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M43" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N43" s="17" t="s">
-        <v>92</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="17"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="8">
-        <v>46285</v>
-      </c>
-      <c r="B44" s="14">
-        <v>420</v>
-      </c>
-      <c r="C44" s="14">
-        <v>20</v>
-      </c>
-      <c r="D44" s="14">
-        <v>120</v>
-      </c>
-      <c r="E44" s="14">
-        <v>180</v>
-      </c>
-      <c r="F44" s="14">
-        <v>0</v>
-      </c>
-      <c r="G44" s="14">
-        <v>0</v>
-      </c>
-      <c r="H44" s="14">
-        <v>30</v>
-      </c>
-      <c r="I44" s="15">
+      <c r="A44" s="13"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>770</v>
-      </c>
-      <c r="J44" s="15">
+        <v/>
+      </c>
+      <c r="J44" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>670</v>
-      </c>
-      <c r="K44" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="L44" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="M44" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="N44" s="17" t="s">
-        <v>95</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+      <c r="M44" s="16"/>
+      <c r="N44" s="17"/>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="8">
-        <v>46286</v>
-      </c>
-      <c r="B45" s="14">
-        <v>420</v>
-      </c>
-      <c r="C45" s="14">
-        <v>30</v>
-      </c>
-      <c r="D45" s="14">
-        <v>180</v>
-      </c>
-      <c r="E45" s="14">
-        <v>90</v>
-      </c>
-      <c r="F45" s="14">
-        <v>240</v>
-      </c>
-      <c r="G45" s="14">
-        <v>4</v>
-      </c>
-      <c r="H45" s="14">
-        <v>60</v>
-      </c>
-      <c r="I45" s="15">
+      <c r="A45" s="13"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15" t="str">
         <f t="shared" si="0"/>
-        <v>1020</v>
-      </c>
-      <c r="J45" s="15">
+        <v/>
+      </c>
+      <c r="J45" s="15" t="str">
         <f t="shared" si="1"/>
-        <v>420</v>
-      </c>
-      <c r="K45" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="L45" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M45" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N45" s="17" t="s">
-        <v>96</v>
-      </c>
+        <v/>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="17"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>
@@ -3482,11 +3410,11 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
       <c r="I70" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
         <v/>
       </c>
       <c r="J70" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
         <v/>
       </c>
       <c r="K70" s="16"/>
@@ -3504,11 +3432,11 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
       <c r="I71" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J71" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K71" s="16"/>
@@ -3526,11 +3454,11 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
       <c r="I72" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J72" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K72" s="16"/>
@@ -3548,11 +3476,11 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
       <c r="I73" s="15" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J73" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K73" s="16"/>
@@ -3570,11 +3498,11 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
       <c r="I74" s="15" t="str">
-        <f t="shared" ref="I74:I137" si="2">IF(SUM(B74:F74,H74)=0,"",SUM(B74:F74,H74))</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
       <c r="J74" s="15" t="str">
-        <f t="shared" ref="J74:J137" si="3">IF(I74="","",1440-I74)</f>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="K74" s="16"/>
@@ -4890,11 +4818,11 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
       <c r="I134" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="I134:I197" si="4">IF(SUM(B134:F134,H134)=0,"",SUM(B134:F134,H134))</f>
         <v/>
       </c>
       <c r="J134" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="J134:J197" si="5">IF(I134="","",1440-I134)</f>
         <v/>
       </c>
       <c r="K134" s="16"/>
@@ -4912,11 +4840,11 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
       <c r="I135" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J135" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K135" s="16"/>
@@ -4934,11 +4862,11 @@
       <c r="G136" s="14"/>
       <c r="H136" s="14"/>
       <c r="I136" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J136" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K136" s="16"/>
@@ -4956,11 +4884,11 @@
       <c r="G137" s="14"/>
       <c r="H137" s="14"/>
       <c r="I137" s="15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J137" s="15" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K137" s="16"/>
@@ -4978,11 +4906,11 @@
       <c r="G138" s="14"/>
       <c r="H138" s="14"/>
       <c r="I138" s="15" t="str">
-        <f t="shared" ref="I138:I201" si="4">IF(SUM(B138:F138,H138)=0,"",SUM(B138:F138,H138))</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
       <c r="J138" s="15" t="str">
-        <f t="shared" ref="J138:J201" si="5">IF(I138="","",1440-I138)</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
       <c r="K138" s="16"/>
@@ -6298,11 +6226,11 @@
       <c r="G198" s="14"/>
       <c r="H198" s="14"/>
       <c r="I198" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" ref="I198:I261" si="6">IF(SUM(B198:F198,H198)=0,"",SUM(B198:F198,H198))</f>
         <v/>
       </c>
       <c r="J198" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="J198:J261" si="7">IF(I198="","",1440-I198)</f>
         <v/>
       </c>
       <c r="K198" s="16"/>
@@ -6320,11 +6248,11 @@
       <c r="G199" s="14"/>
       <c r="H199" s="14"/>
       <c r="I199" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J199" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K199" s="16"/>
@@ -6342,11 +6270,11 @@
       <c r="G200" s="14"/>
       <c r="H200" s="14"/>
       <c r="I200" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J200" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K200" s="16"/>
@@ -6364,11 +6292,11 @@
       <c r="G201" s="14"/>
       <c r="H201" s="14"/>
       <c r="I201" s="15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J201" s="15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K201" s="16"/>
@@ -6386,11 +6314,11 @@
       <c r="G202" s="14"/>
       <c r="H202" s="14"/>
       <c r="I202" s="15" t="str">
-        <f t="shared" ref="I202:I265" si="6">IF(SUM(B202:F202,H202)=0,"",SUM(B202:F202,H202))</f>
+        <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="J202" s="15" t="str">
-        <f t="shared" ref="J202:J265" si="7">IF(I202="","",1440-I202)</f>
+        <f t="shared" si="7"/>
         <v/>
       </c>
       <c r="K202" s="16"/>
@@ -7706,11 +7634,11 @@
       <c r="G262" s="14"/>
       <c r="H262" s="14"/>
       <c r="I262" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="I262:I325" si="8">IF(SUM(B262:F262,H262)=0,"",SUM(B262:F262,H262))</f>
         <v/>
       </c>
       <c r="J262" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="J262:J325" si="9">IF(I262="","",1440-I262)</f>
         <v/>
       </c>
       <c r="K262" s="16"/>
@@ -7728,11 +7656,11 @@
       <c r="G263" s="14"/>
       <c r="H263" s="14"/>
       <c r="I263" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J263" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K263" s="16"/>
@@ -7750,11 +7678,11 @@
       <c r="G264" s="14"/>
       <c r="H264" s="14"/>
       <c r="I264" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J264" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K264" s="16"/>
@@ -7772,11 +7700,11 @@
       <c r="G265" s="14"/>
       <c r="H265" s="14"/>
       <c r="I265" s="15" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J265" s="15" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K265" s="16"/>
@@ -7794,11 +7722,11 @@
       <c r="G266" s="14"/>
       <c r="H266" s="14"/>
       <c r="I266" s="15" t="str">
-        <f t="shared" ref="I266:I329" si="8">IF(SUM(B266:F266,H266)=0,"",SUM(B266:F266,H266))</f>
+        <f t="shared" si="8"/>
         <v/>
       </c>
       <c r="J266" s="15" t="str">
-        <f t="shared" ref="J266:J329" si="9">IF(I266="","",1440-I266)</f>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="K266" s="16"/>
@@ -9114,11 +9042,11 @@
       <c r="G326" s="14"/>
       <c r="H326" s="14"/>
       <c r="I326" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="I326:I389" si="10">IF(SUM(B326:F326,H326)=0,"",SUM(B326:F326,H326))</f>
         <v/>
       </c>
       <c r="J326" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="J326:J389" si="11">IF(I326="","",1440-I326)</f>
         <v/>
       </c>
       <c r="K326" s="16"/>
@@ -9136,11 +9064,11 @@
       <c r="G327" s="14"/>
       <c r="H327" s="14"/>
       <c r="I327" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J327" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K327" s="16"/>
@@ -9158,11 +9086,11 @@
       <c r="G328" s="14"/>
       <c r="H328" s="14"/>
       <c r="I328" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J328" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K328" s="16"/>
@@ -9180,11 +9108,11 @@
       <c r="G329" s="14"/>
       <c r="H329" s="14"/>
       <c r="I329" s="15" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J329" s="15" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K329" s="16"/>
@@ -9202,11 +9130,11 @@
       <c r="G330" s="14"/>
       <c r="H330" s="14"/>
       <c r="I330" s="15" t="str">
-        <f t="shared" ref="I330:I393" si="10">IF(SUM(B330:F330,H330)=0,"",SUM(B330:F330,H330))</f>
+        <f t="shared" si="10"/>
         <v/>
       </c>
       <c r="J330" s="15" t="str">
-        <f t="shared" ref="J330:J393" si="11">IF(I330="","",1440-I330)</f>
+        <f t="shared" si="11"/>
         <v/>
       </c>
       <c r="K330" s="16"/>
@@ -10522,11 +10450,11 @@
       <c r="G390" s="14"/>
       <c r="H390" s="14"/>
       <c r="I390" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="I390:I401" si="12">IF(SUM(B390:F390,H390)=0,"",SUM(B390:F390,H390))</f>
         <v/>
       </c>
       <c r="J390" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" ref="J390:J401" si="13">IF(I390="","",1440-I390)</f>
         <v/>
       </c>
       <c r="K390" s="16"/>
@@ -10544,11 +10472,11 @@
       <c r="G391" s="14"/>
       <c r="H391" s="14"/>
       <c r="I391" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J391" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K391" s="16"/>
@@ -10566,11 +10494,11 @@
       <c r="G392" s="14"/>
       <c r="H392" s="14"/>
       <c r="I392" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J392" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K392" s="16"/>
@@ -10588,11 +10516,11 @@
       <c r="G393" s="14"/>
       <c r="H393" s="14"/>
       <c r="I393" s="15" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J393" s="15" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K393" s="16"/>
@@ -10610,11 +10538,11 @@
       <c r="G394" s="14"/>
       <c r="H394" s="14"/>
       <c r="I394" s="15" t="str">
-        <f t="shared" ref="I394:I405" si="12">IF(SUM(B394:F394,H394)=0,"",SUM(B394:F394,H394))</f>
+        <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="J394" s="15" t="str">
-        <f t="shared" ref="J394:J405" si="13">IF(I394="","",1440-I394)</f>
+        <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="K394" s="16"/>
@@ -10776,94 +10704,6 @@
       <c r="M401" s="16"/>
       <c r="N401" s="17"/>
     </row>
-    <row r="402" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A402" s="13"/>
-      <c r="B402" s="14"/>
-      <c r="C402" s="14"/>
-      <c r="D402" s="14"/>
-      <c r="E402" s="14"/>
-      <c r="F402" s="14"/>
-      <c r="G402" s="14"/>
-      <c r="H402" s="14"/>
-      <c r="I402" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J402" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K402" s="16"/>
-      <c r="L402" s="16"/>
-      <c r="M402" s="16"/>
-      <c r="N402" s="17"/>
-    </row>
-    <row r="403" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A403" s="13"/>
-      <c r="B403" s="14"/>
-      <c r="C403" s="14"/>
-      <c r="D403" s="14"/>
-      <c r="E403" s="14"/>
-      <c r="F403" s="14"/>
-      <c r="G403" s="14"/>
-      <c r="H403" s="14"/>
-      <c r="I403" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J403" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K403" s="16"/>
-      <c r="L403" s="16"/>
-      <c r="M403" s="16"/>
-      <c r="N403" s="17"/>
-    </row>
-    <row r="404" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A404" s="13"/>
-      <c r="B404" s="14"/>
-      <c r="C404" s="14"/>
-      <c r="D404" s="14"/>
-      <c r="E404" s="14"/>
-      <c r="F404" s="14"/>
-      <c r="G404" s="14"/>
-      <c r="H404" s="14"/>
-      <c r="I404" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J404" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K404" s="16"/>
-      <c r="L404" s="16"/>
-      <c r="M404" s="16"/>
-      <c r="N404" s="17"/>
-    </row>
-    <row r="405" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A405" s="13"/>
-      <c r="B405" s="14"/>
-      <c r="C405" s="14"/>
-      <c r="D405" s="14"/>
-      <c r="E405" s="14"/>
-      <c r="F405" s="14"/>
-      <c r="G405" s="14"/>
-      <c r="H405" s="14"/>
-      <c r="I405" s="15" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="J405" s="15" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="K405" s="16"/>
-      <c r="L405" s="16"/>
-      <c r="M405" s="16"/>
-      <c r="N405" s="17"/>
-    </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="A4:N4"/>
@@ -10873,21 +10713,21 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J405">
+  <conditionalFormatting sqref="J6:J401">
     <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K405" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" error="Please choose a value from the dropdown list." prompt="Select today's overall feeling" sqref="K6:K401" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"Excellent,Good,Neutral,Low,Stressed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L405" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's satisfaction level" sqref="L6:L401" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"Very Satisfied,Satisfied,Neutral,Unsatisfied,Very Unsatisfied"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M405" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" prompt="Select today's energy level" sqref="M6:M401" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"High,Medium,Low"</formula1>
       <formula2>0</formula2>
     </dataValidation>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A3F99A-A21A-4B16-9115-20A5B206E924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353103CA-AB61-4A93-9C70-052A73C7C798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2807,26 +2807,50 @@
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+      <c r="A43" s="8">
+        <v>46288</v>
+      </c>
+      <c r="B43" s="14">
+        <v>420</v>
+      </c>
+      <c r="C43" s="14">
+        <v>60</v>
+      </c>
+      <c r="D43" s="14">
+        <v>180</v>
+      </c>
+      <c r="E43" s="14">
+        <v>120</v>
+      </c>
+      <c r="F43" s="14">
+        <v>300</v>
+      </c>
+      <c r="G43" s="14">
+        <v>5</v>
+      </c>
+      <c r="H43" s="14">
+        <v>60</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>1140</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>300</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{353103CA-AB61-4A93-9C70-052A73C7C798}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E0FEBD-8078-4B79-AF36-53F4E906FB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2853,26 +2853,50 @@
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+      <c r="A44" s="8">
+        <v>46289</v>
+      </c>
+      <c r="B44" s="14">
+        <v>380</v>
+      </c>
+      <c r="C44" s="14">
+        <v>120</v>
+      </c>
+      <c r="D44" s="14">
+        <v>120</v>
+      </c>
+      <c r="E44" s="14">
+        <v>60</v>
+      </c>
+      <c r="F44" s="14">
+        <v>360</v>
+      </c>
+      <c r="G44" s="14">
+        <v>6</v>
+      </c>
+      <c r="H44" s="14">
+        <v>30</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>370</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7E0FEBD-8078-4B79-AF36-53F4E906FB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37BAF46-1ECB-4984-B3DB-C93BB794B849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2899,26 +2899,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B45" s="14">
+        <v>320</v>
+      </c>
+      <c r="C45" s="14">
+        <v>45</v>
+      </c>
+      <c r="D45" s="14">
+        <v>180</v>
+      </c>
+      <c r="E45" s="14">
+        <v>120</v>
+      </c>
+      <c r="F45" s="14">
+        <v>420</v>
+      </c>
+      <c r="G45" s="14">
+        <v>7</v>
+      </c>
+      <c r="H45" s="14">
+        <v>60</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>1145</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>295</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37BAF46-1ECB-4984-B3DB-C93BB794B849}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033059BE-D7D0-4DB1-813D-E796BDF3A999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -2945,26 +2945,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="8">
+        <v>46291</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>30</v>
+      </c>
+      <c r="D46" s="14">
+        <v>320</v>
+      </c>
+      <c r="E46" s="14">
+        <v>240</v>
+      </c>
+      <c r="F46" s="14">
+        <v>0</v>
+      </c>
+      <c r="G46" s="14">
+        <v>0</v>
+      </c>
+      <c r="H46" s="14">
+        <v>120</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033059BE-D7D0-4DB1-813D-E796BDF3A999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>fever.</t>
+  </si>
+  <si>
+    <t>bad day.</t>
   </si>
 </sst>
 </file>
@@ -2991,26 +2994,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="8">
+        <v>46292</v>
+      </c>
+      <c r="B47" s="14">
+        <v>360</v>
+      </c>
+      <c r="C47" s="14">
+        <v>60</v>
+      </c>
+      <c r="D47" s="14">
+        <v>120</v>
+      </c>
+      <c r="E47" s="14">
+        <v>320</v>
+      </c>
+      <c r="F47" s="14">
+        <v>0</v>
+      </c>
+      <c r="G47" s="14">
+        <v>0</v>
+      </c>
+      <c r="H47" s="14">
+        <v>45</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>905</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>535</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54D0C80A-AF27-436C-BA7B-C6B860FBF886}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -332,6 +332,9 @@
   <si>
     <t>bad day.</t>
   </si>
+  <si>
+    <t>stressful day</t>
+  </si>
 </sst>
 </file>
 
@@ -517,7 +520,19 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="2">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+        <name val="Arial"/>
+        <charset val="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3040,26 +3055,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="8">
+        <v>46293</v>
+      </c>
+      <c r="B48" s="14">
+        <v>180</v>
+      </c>
+      <c r="C48" s="14">
+        <v>20</v>
+      </c>
+      <c r="D48" s="14">
+        <v>180</v>
+      </c>
+      <c r="E48" s="14">
+        <v>120</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>360</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>860</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>580</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>
@@ -10836,8 +10875,13 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J401">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="J6:J47 J49:J401">
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54D0C80A-AF27-436C-BA7B-C6B860FBF886}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88CCC49A-8995-4F14-A185-439B21126C7B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -626,6 +626,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3101,26 +3105,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="8">
+        <v>46294</v>
+      </c>
+      <c r="B49" s="14">
+        <v>60</v>
+      </c>
+      <c r="C49" s="14">
+        <v>30</v>
+      </c>
+      <c r="D49" s="14">
+        <v>120</v>
+      </c>
+      <c r="E49" s="14">
+        <v>220</v>
+      </c>
+      <c r="F49" s="14">
+        <v>0</v>
+      </c>
+      <c r="G49" s="14">
+        <v>0</v>
+      </c>
+      <c r="H49" s="14">
+        <v>220</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>650</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>790</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
@@ -10875,12 +10903,12 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J47 J49:J401">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="lessThan">
+  <conditionalFormatting sqref="J6:J48 J50:J401">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48">
+  <conditionalFormatting sqref="J49">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{88CCC49A-8995-4F14-A185-439B21126C7B}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD2CD083-D0B1-435C-A978-D494B5D6757B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -335,6 +335,9 @@
   <si>
     <t>stressful day</t>
   </si>
+  <si>
+    <t>Not a good day.</t>
+  </si>
 </sst>
 </file>
 
@@ -520,19 +523,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-        <name val="Arial"/>
-        <charset val="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -3151,26 +3142,50 @@
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+      <c r="A50" s="8">
+        <v>46295</v>
+      </c>
+      <c r="B50" s="14">
+        <v>420</v>
+      </c>
+      <c r="C50" s="14">
+        <v>45</v>
+      </c>
+      <c r="D50" s="14">
+        <v>360</v>
+      </c>
+      <c r="E50" s="14">
+        <v>180</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>120</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>1125</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>315</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
@@ -10903,12 +10918,7 @@
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="F3:G3"/>
   </mergeCells>
-  <conditionalFormatting sqref="J6:J48 J50:J401">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J49">
+  <conditionalFormatting sqref="J6:J401">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AD2CD083-D0B1-435C-A978-D494B5D6757B}"/>
+  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A101A8-FEEB-441B-9FC9-BFB6140931BA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t>Not a good day.</t>
+  </si>
+  <si>
+    <t>feeling low.</t>
   </si>
 </sst>
 </file>
@@ -3188,26 +3191,50 @@
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+      <c r="A51" s="8">
+        <v>46296</v>
+      </c>
+      <c r="B51" s="14">
+        <v>380</v>
+      </c>
+      <c r="C51" s="14">
+        <v>60</v>
+      </c>
+      <c r="D51" s="14">
+        <v>260</v>
+      </c>
+      <c r="E51" s="14">
+        <v>180</v>
+      </c>
+      <c r="F51" s="14">
+        <v>0</v>
+      </c>
+      <c r="G51" s="14">
+        <v>0</v>
+      </c>
+      <c r="H51" s="14">
+        <v>180</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="29" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44A101A8-FEEB-441B-9FC9-BFB6140931BA}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3270B2CF-1697-4276-8518-1962E603B3E1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3237,26 +3237,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="8">
+        <v>46297</v>
+      </c>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>45</v>
+      </c>
+      <c r="D52" s="14">
+        <v>240</v>
+      </c>
+      <c r="E52" s="14">
+        <v>240</v>
+      </c>
+      <c r="F52" s="14">
+        <v>0</v>
+      </c>
+      <c r="G52" s="14">
+        <v>0</v>
+      </c>
+      <c r="H52" s="14">
+        <v>60</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1005</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>435</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3270B2CF-1697-4276-8518-1962E603B3E1}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D22826C6-BF4F-4F46-916F-3CA189127FC5}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>feeling low.</t>
+  </si>
+  <si>
+    <t>fruitful day.</t>
   </si>
 </sst>
 </file>
@@ -3283,26 +3286,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="8">
+        <v>46298</v>
+      </c>
+      <c r="B53" s="14">
+        <v>480</v>
+      </c>
+      <c r="C53" s="14">
+        <v>30</v>
+      </c>
+      <c r="D53" s="14">
+        <v>300</v>
+      </c>
+      <c r="E53" s="14">
+        <v>120</v>
+      </c>
+      <c r="F53" s="14">
+        <v>0</v>
+      </c>
+      <c r="G53" s="14">
+        <v>0</v>
+      </c>
+      <c r="H53" s="14">
+        <v>120</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1050</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>390</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D22826C6-BF4F-4F46-916F-3CA189127FC5}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28DA3548-7F03-4D14-ACAC-B0D1DC0220D7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>fruitful day.</t>
+  </si>
+  <si>
+    <t>stressed day.</t>
   </si>
 </sst>
 </file>
@@ -3332,26 +3335,50 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+      <c r="A54" s="8">
+        <v>46299</v>
+      </c>
+      <c r="B54" s="14">
+        <v>380</v>
+      </c>
+      <c r="C54" s="14">
+        <v>45</v>
+      </c>
+      <c r="D54" s="14">
+        <v>240</v>
+      </c>
+      <c r="E54" s="14">
+        <v>180</v>
+      </c>
+      <c r="F54" s="14">
+        <v>0</v>
+      </c>
+      <c r="G54" s="14">
+        <v>0</v>
+      </c>
+      <c r="H54" s="14">
+        <v>120</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>965</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>475</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{28DA3548-7F03-4D14-ACAC-B0D1DC0220D7}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{993C8FD6-97AB-4CF9-8216-CB034E46258E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3381,26 +3381,50 @@
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+      <c r="A55" s="8">
+        <v>46300</v>
+      </c>
+      <c r="B55" s="14">
+        <v>420</v>
+      </c>
+      <c r="C55" s="14">
+        <v>60</v>
+      </c>
+      <c r="D55" s="14">
+        <v>260</v>
+      </c>
+      <c r="E55" s="14">
+        <v>120</v>
+      </c>
+      <c r="F55" s="14">
+        <v>240</v>
+      </c>
+      <c r="G55" s="14">
+        <v>4</v>
+      </c>
+      <c r="H55" s="14">
+        <v>80</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>260</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A56" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{993C8FD6-97AB-4CF9-8216-CB034E46258E}"/>
+  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{273B6BD2-1541-4A0C-8079-8447FBD507B3}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>stressed day.</t>
+  </si>
+  <si>
+    <t>hectic day.</t>
   </si>
 </sst>
 </file>
@@ -3427,26 +3430,50 @@
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="8">
+        <v>46301</v>
+      </c>
+      <c r="B56" s="14">
+        <v>320</v>
+      </c>
+      <c r="C56" s="14">
+        <v>45</v>
+      </c>
+      <c r="D56" s="14">
+        <v>120</v>
+      </c>
+      <c r="E56" s="14">
+        <v>180</v>
+      </c>
+      <c r="F56" s="14">
+        <v>300</v>
+      </c>
+      <c r="G56" s="14">
+        <v>5</v>
+      </c>
+      <c r="H56" s="14">
+        <v>60</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>1025</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+        <v>415</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N56" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="92" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{273B6BD2-1541-4A0C-8079-8447FBD507B3}"/>
+  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F5E556-63F7-4196-8F8A-A492904DED9B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,6 +349,9 @@
   </si>
   <si>
     <t>hectic day.</t>
+  </si>
+  <si>
+    <t>working day.</t>
   </si>
 </sst>
 </file>
@@ -3476,26 +3479,50 @@
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+      <c r="A57" s="8">
+        <v>46302</v>
+      </c>
+      <c r="B57" s="14">
+        <v>380</v>
+      </c>
+      <c r="C57" s="14">
+        <v>30</v>
+      </c>
+      <c r="D57" s="14">
+        <v>120</v>
+      </c>
+      <c r="E57" s="14">
+        <v>240</v>
+      </c>
+      <c r="F57" s="14">
+        <v>300</v>
+      </c>
+      <c r="G57" s="14">
+        <v>5</v>
+      </c>
+      <c r="H57" s="14">
+        <v>120</v>
+      </c>
+      <c r="I57" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1190</v>
+      </c>
+      <c r="J57" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
+        <v>250</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A58" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6F5E556-63F7-4196-8F8A-A492904DED9B}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EB7D141-90F5-4236-B641-AE4BE157CFC7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="105">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3525,26 +3525,50 @@
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+      <c r="A58" s="8">
+        <v>46303</v>
+      </c>
+      <c r="B58" s="14">
+        <v>420</v>
+      </c>
+      <c r="C58" s="14">
+        <v>40</v>
+      </c>
+      <c r="D58" s="14">
+        <v>140</v>
+      </c>
+      <c r="E58" s="14">
+        <v>320</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>160</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A59" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="117" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EB7D141-90F5-4236-B641-AE4BE157CFC7}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59C3B4F4-57B5-419D-8B3B-8639C6112D9E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -352,6 +352,9 @@
   </si>
   <si>
     <t>working day.</t>
+  </si>
+  <si>
+    <t>travelling.</t>
   </si>
 </sst>
 </file>
@@ -3571,29 +3574,53 @@
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
+      <c r="A59" s="8">
+        <v>46304</v>
+      </c>
+      <c r="B59" s="14">
+        <v>320</v>
+      </c>
+      <c r="C59" s="14">
+        <v>20</v>
+      </c>
+      <c r="D59" s="14">
+        <v>120</v>
+      </c>
+      <c r="E59" s="14">
+        <v>180</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>420</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
+      <c r="A60" s="8"/>
       <c r="B60" s="14"/>
       <c r="C60" s="14"/>
       <c r="D60" s="14"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{59C3B4F4-57B5-419D-8B3B-8639C6112D9E}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDB75D5-FA02-404D-A848-161C39A2C6B1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3620,26 +3620,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="8"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="8">
+        <v>46305</v>
+      </c>
+      <c r="B60" s="14">
+        <v>420</v>
+      </c>
+      <c r="C60" s="14">
+        <v>60</v>
+      </c>
+      <c r="D60" s="14">
+        <v>320</v>
+      </c>
+      <c r="E60" s="14">
+        <v>120</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>120</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFDB75D5-FA02-404D-A848-161C39A2C6B1}"/>
+  <xr:revisionPtr revIDLastSave="159" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{865FC204-A635-41BD-983D-924EC717498A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>travelling.</t>
+  </si>
+  <si>
+    <t>prepared for mid term.</t>
   </si>
 </sst>
 </file>
@@ -3666,26 +3669,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="8">
+        <v>46306</v>
+      </c>
+      <c r="B61" s="14">
+        <v>320</v>
+      </c>
+      <c r="C61" s="14">
+        <v>120</v>
+      </c>
+      <c r="D61" s="14">
+        <v>420</v>
+      </c>
+      <c r="E61" s="14">
+        <v>240</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>160</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>1260</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>180</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="159" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{865FC204-A635-41BD-983D-924EC717498A}"/>
+  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{435983E4-B1EC-4B8C-94CE-7C91672A28D1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -638,10 +638,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3691,15 +3687,15 @@
         <v>0</v>
       </c>
       <c r="H61" s="14">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v>1260</v>
+        <v>1220</v>
       </c>
       <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="K61" s="16" t="s">
         <v>55</v>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="162" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{435983E4-B1EC-4B8C-94CE-7C91672A28D1}"/>
+  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D4ACF35-E720-4EF3-84AC-C7C8AA74DCF1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -359,6 +359,9 @@
   <si>
     <t>prepared for mid term.</t>
   </si>
+  <si>
+    <t>exams.</t>
+  </si>
 </sst>
 </file>
 
@@ -638,6 +641,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -3711,26 +3718,50 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A62" s="13"/>
-      <c r="B62" s="14"/>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15" t="str">
+      <c r="A62" s="8">
+        <v>46307</v>
+      </c>
+      <c r="B62" s="14">
+        <v>380</v>
+      </c>
+      <c r="C62" s="14">
+        <v>45</v>
+      </c>
+      <c r="D62" s="14">
+        <v>380</v>
+      </c>
+      <c r="E62" s="14">
+        <v>210</v>
+      </c>
+      <c r="F62" s="14">
+        <v>0</v>
+      </c>
+      <c r="G62" s="14">
+        <v>0</v>
+      </c>
+      <c r="H62" s="14">
+        <v>180</v>
+      </c>
+      <c r="I62" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J62" s="15" t="str">
+        <v>1195</v>
+      </c>
+      <c r="J62" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K62" s="16"/>
-      <c r="L62" s="16"/>
-      <c r="M62" s="16"/>
-      <c r="N62" s="17"/>
+        <v>245</v>
+      </c>
+      <c r="K62" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L62" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M62" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N62" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A63" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="175" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D4ACF35-E720-4EF3-84AC-C7C8AA74DCF1}"/>
+  <xr:revisionPtr revIDLastSave="188" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27EAEF44-2718-473B-96C7-613A15562A3C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t>exams.</t>
+  </si>
+  <si>
+    <t>today is c++ exam.</t>
   </si>
 </sst>
 </file>
@@ -3764,26 +3767,50 @@
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A63" s="13"/>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15" t="str">
+      <c r="A63" s="8">
+        <v>46308</v>
+      </c>
+      <c r="B63" s="14">
+        <v>420</v>
+      </c>
+      <c r="C63" s="14">
+        <v>60</v>
+      </c>
+      <c r="D63" s="14">
+        <v>320</v>
+      </c>
+      <c r="E63" s="14">
+        <v>120</v>
+      </c>
+      <c r="F63" s="14">
+        <v>0</v>
+      </c>
+      <c r="G63" s="14">
+        <v>0</v>
+      </c>
+      <c r="H63" s="14">
+        <v>380</v>
+      </c>
+      <c r="I63" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J63" s="15" t="str">
+        <v>1300</v>
+      </c>
+      <c r="J63" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K63" s="16"/>
-      <c r="L63" s="16"/>
-      <c r="M63" s="16"/>
-      <c r="N63" s="17"/>
+        <v>140</v>
+      </c>
+      <c r="K63" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L63" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="M63" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N63" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A64" s="13"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11A6B5A1-AB15-4343-BEBC-6F699A0E9AC7}"/>
+  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAFA882E-0A47-41A9-AE70-E60533D46677}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t>today is c++ exam.</t>
+  </si>
+  <si>
+    <t>prepare for my exam.</t>
   </si>
 </sst>
 </file>
@@ -3856,26 +3859,50 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A65" s="8"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="13"/>
-      <c r="H65" s="13"/>
-      <c r="I65" s="14" t="str">
+      <c r="A65" s="8">
+        <v>46310</v>
+      </c>
+      <c r="B65" s="13">
+        <v>380</v>
+      </c>
+      <c r="C65" s="13">
+        <v>60</v>
+      </c>
+      <c r="D65" s="13">
+        <v>480</v>
+      </c>
+      <c r="E65" s="13">
+        <v>120</v>
+      </c>
+      <c r="F65" s="13">
+        <v>0</v>
+      </c>
+      <c r="G65" s="13">
+        <v>0</v>
+      </c>
+      <c r="H65" s="13">
+        <v>60</v>
+      </c>
+      <c r="I65" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J65" s="14" t="str">
+        <v>1100</v>
+      </c>
+      <c r="J65" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K65" s="15"/>
-      <c r="L65" s="15"/>
-      <c r="M65" s="15"/>
-      <c r="N65" s="16"/>
+        <v>340</v>
+      </c>
+      <c r="K65" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L65" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M65" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N65" s="16" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A66" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="216" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CAFA882E-0A47-41A9-AE70-E60533D46677}"/>
+  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A357E807-8872-4FF5-810D-4AF7E499E4AA}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>prepare for my exam.</t>
+  </si>
+  <si>
+    <t>today is my exam.</t>
   </si>
 </sst>
 </file>
@@ -3905,26 +3908,50 @@
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A66" s="8"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="13"/>
-      <c r="H66" s="13"/>
-      <c r="I66" s="14" t="str">
+      <c r="A66" s="8">
+        <v>46311</v>
+      </c>
+      <c r="B66" s="13">
+        <v>420</v>
+      </c>
+      <c r="C66" s="13">
+        <v>45</v>
+      </c>
+      <c r="D66" s="13">
+        <v>380</v>
+      </c>
+      <c r="E66" s="13">
+        <v>220</v>
+      </c>
+      <c r="F66" s="13">
+        <v>0</v>
+      </c>
+      <c r="G66" s="13">
+        <v>0</v>
+      </c>
+      <c r="H66" s="13">
+        <v>120</v>
+      </c>
+      <c r="I66" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J66" s="14" t="str">
+        <v>1185</v>
+      </c>
+      <c r="J66" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K66" s="15"/>
-      <c r="L66" s="15"/>
-      <c r="M66" s="15"/>
-      <c r="N66" s="16"/>
+        <v>255</v>
+      </c>
+      <c r="K66" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L66" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="M66" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N66" s="16" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A67" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="229" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A357E807-8872-4FF5-810D-4AF7E499E4AA}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBB5B413-C154-432A-9BB7-D256A11B76BC}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -370,6 +370,9 @@
   </si>
   <si>
     <t>today is my exam.</t>
+  </si>
+  <si>
+    <t>beautiful day.</t>
   </si>
 </sst>
 </file>
@@ -3954,26 +3957,50 @@
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A67" s="8"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="13"/>
-      <c r="H67" s="13"/>
-      <c r="I67" s="14" t="str">
+      <c r="A67" s="8">
+        <v>46312</v>
+      </c>
+      <c r="B67" s="13">
+        <v>410</v>
+      </c>
+      <c r="C67" s="13">
+        <v>120</v>
+      </c>
+      <c r="D67" s="13">
+        <v>320</v>
+      </c>
+      <c r="E67" s="13">
+        <v>240</v>
+      </c>
+      <c r="F67" s="13">
+        <v>0</v>
+      </c>
+      <c r="G67" s="13">
+        <v>0</v>
+      </c>
+      <c r="H67" s="13">
+        <v>180</v>
+      </c>
+      <c r="I67" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J67" s="14" t="str">
+        <v>1270</v>
+      </c>
+      <c r="J67" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="16"/>
+        <v>170</v>
+      </c>
+      <c r="K67" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L67" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M67" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N67" s="16" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A68" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="241" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CBB5B413-C154-432A-9BB7-D256A11B76BC}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECC79F9-5646-4558-AD47-46228240BDEF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4003,26 +4003,50 @@
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A68" s="8"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="13"/>
-      <c r="H68" s="13"/>
-      <c r="I68" s="14" t="str">
+      <c r="A68" s="8">
+        <v>46313</v>
+      </c>
+      <c r="B68" s="13">
+        <v>420</v>
+      </c>
+      <c r="C68" s="13">
+        <v>60</v>
+      </c>
+      <c r="D68" s="13">
+        <v>180</v>
+      </c>
+      <c r="E68" s="13">
+        <v>120</v>
+      </c>
+      <c r="F68" s="13">
+        <v>0</v>
+      </c>
+      <c r="G68" s="13">
+        <v>0</v>
+      </c>
+      <c r="H68" s="13">
+        <v>120</v>
+      </c>
+      <c r="I68" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J68" s="14" t="str">
+        <v>900</v>
+      </c>
+      <c r="J68" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K68" s="15"/>
-      <c r="L68" s="15"/>
-      <c r="M68" s="15"/>
-      <c r="N68" s="16"/>
+        <v>540</v>
+      </c>
+      <c r="K68" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L68" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M68" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N68" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A69" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2ECC79F9-5646-4558-AD47-46228240BDEF}"/>
+  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D9BBB91-99C7-4CFE-9A88-6C9C93F31967}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4049,26 +4049,50 @@
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A69" s="8"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="13"/>
-      <c r="H69" s="13"/>
-      <c r="I69" s="14" t="str">
+      <c r="A69" s="8">
+        <v>46314</v>
+      </c>
+      <c r="B69" s="13">
+        <v>320</v>
+      </c>
+      <c r="C69" s="13">
+        <v>50</v>
+      </c>
+      <c r="D69" s="13">
+        <v>120</v>
+      </c>
+      <c r="E69" s="13">
+        <v>240</v>
+      </c>
+      <c r="F69" s="13">
+        <v>240</v>
+      </c>
+      <c r="G69" s="13">
+        <v>4</v>
+      </c>
+      <c r="H69" s="13">
+        <v>210</v>
+      </c>
+      <c r="I69" s="14">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J69" s="14" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J69" s="14">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K69" s="15"/>
-      <c r="L69" s="15"/>
-      <c r="M69" s="15"/>
-      <c r="N69" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K69" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L69" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M69" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N69" s="16" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A70" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="265" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D9BBB91-99C7-4CFE-9A88-6C9C93F31967}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBAB527F-DD16-49EE-A232-CF8875613B01}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="112">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4095,26 +4095,50 @@
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A70" s="8"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="13"/>
-      <c r="H70" s="13"/>
-      <c r="I70" s="14" t="str">
+      <c r="A70" s="8">
+        <v>46315</v>
+      </c>
+      <c r="B70" s="13">
+        <v>420</v>
+      </c>
+      <c r="C70" s="13">
+        <v>60</v>
+      </c>
+      <c r="D70" s="13">
+        <v>140</v>
+      </c>
+      <c r="E70" s="13">
+        <v>280</v>
+      </c>
+      <c r="F70" s="13">
+        <v>0</v>
+      </c>
+      <c r="G70" s="13">
+        <v>0</v>
+      </c>
+      <c r="H70" s="13">
+        <v>320</v>
+      </c>
+      <c r="I70" s="14">
         <f t="shared" ref="I70:I133" si="2">IF(SUM(B70:F70,H70)=0,"",SUM(B70:F70,H70))</f>
-        <v/>
-      </c>
-      <c r="J70" s="14" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J70" s="14">
         <f t="shared" ref="J70:J133" si="3">IF(I70="","",1440-I70)</f>
-        <v/>
-      </c>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
-      <c r="N70" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K70" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L70" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M70" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N70" s="16" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A71" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="278" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BBAB527F-DD16-49EE-A232-CF8875613B01}"/>
+  <xr:revisionPtr revIDLastSave="290" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B6BD24D-CA61-4BF6-A1F2-DDB01A96105C}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -373,6 +373,9 @@
   </si>
   <si>
     <t>beautiful day.</t>
+  </si>
+  <si>
+    <t>today is nice day.</t>
   </si>
 </sst>
 </file>
@@ -4141,26 +4144,50 @@
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A71" s="8"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="13"/>
-      <c r="H71" s="13"/>
-      <c r="I71" s="14" t="str">
+      <c r="A71" s="8">
+        <v>46316</v>
+      </c>
+      <c r="B71" s="13">
+        <v>380</v>
+      </c>
+      <c r="C71" s="13">
+        <v>80</v>
+      </c>
+      <c r="D71" s="13">
+        <v>120</v>
+      </c>
+      <c r="E71" s="13">
+        <v>120</v>
+      </c>
+      <c r="F71" s="13">
+        <v>300</v>
+      </c>
+      <c r="G71" s="13">
+        <v>5</v>
+      </c>
+      <c r="H71" s="13">
+        <v>180</v>
+      </c>
+      <c r="I71" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J71" s="14" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J71" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K71" s="15"/>
-      <c r="L71" s="15"/>
-      <c r="M71" s="15"/>
-      <c r="N71" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L71" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M71" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N71" s="16" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A72" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="290" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B6BD24D-CA61-4BF6-A1F2-DDB01A96105C}"/>
+  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31925C18-AF62-42A2-88F2-8411498122E6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4190,26 +4190,50 @@
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A72" s="8"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="13"/>
-      <c r="H72" s="13"/>
-      <c r="I72" s="14" t="str">
+      <c r="A72" s="8">
+        <v>46317</v>
+      </c>
+      <c r="B72" s="13">
+        <v>320</v>
+      </c>
+      <c r="C72" s="13">
+        <v>30</v>
+      </c>
+      <c r="D72" s="13">
+        <v>180</v>
+      </c>
+      <c r="E72" s="13">
+        <v>60</v>
+      </c>
+      <c r="F72" s="13">
+        <v>360</v>
+      </c>
+      <c r="G72" s="13">
+        <v>6</v>
+      </c>
+      <c r="H72" s="13">
+        <v>120</v>
+      </c>
+      <c r="I72" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J72" s="14" t="str">
+        <v>1070</v>
+      </c>
+      <c r="J72" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K72" s="15"/>
-      <c r="L72" s="15"/>
-      <c r="M72" s="15"/>
-      <c r="N72" s="16"/>
+        <v>370</v>
+      </c>
+      <c r="K72" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L72" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M72" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N72" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A73" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="302" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31925C18-AF62-42A2-88F2-8411498122E6}"/>
+  <xr:revisionPtr revIDLastSave="315" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{415332E1-C1D1-4F6E-B682-22D9DD6D752D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4236,26 +4236,50 @@
       </c>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A73" s="8"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="13"/>
-      <c r="H73" s="13"/>
-      <c r="I73" s="14" t="str">
+      <c r="A73" s="8">
+        <v>46318</v>
+      </c>
+      <c r="B73" s="13">
+        <v>420</v>
+      </c>
+      <c r="C73" s="13">
+        <v>60</v>
+      </c>
+      <c r="D73" s="13">
+        <v>120</v>
+      </c>
+      <c r="E73" s="13">
+        <v>180</v>
+      </c>
+      <c r="F73" s="13">
+        <v>420</v>
+      </c>
+      <c r="G73" s="13">
+        <v>7</v>
+      </c>
+      <c r="H73" s="13">
+        <v>30</v>
+      </c>
+      <c r="I73" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J73" s="14" t="str">
+        <v>1230</v>
+      </c>
+      <c r="J73" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K73" s="15"/>
-      <c r="L73" s="15"/>
-      <c r="M73" s="15"/>
-      <c r="N73" s="16"/>
+        <v>210</v>
+      </c>
+      <c r="K73" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L73" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M73" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N73" s="16" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A74" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="315" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{415332E1-C1D1-4F6E-B682-22D9DD6D752D}"/>
+  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41791DD6-4198-47C1-B1DA-78C7E1E0DE39}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -376,6 +376,9 @@
   </si>
   <si>
     <t>today is nice day.</t>
+  </si>
+  <si>
+    <t>better than yesterday.</t>
   </si>
 </sst>
 </file>
@@ -4282,26 +4285,50 @@
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A74" s="8"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="13"/>
-      <c r="H74" s="13"/>
-      <c r="I74" s="14" t="str">
+      <c r="A74" s="8">
+        <v>46319</v>
+      </c>
+      <c r="B74" s="13">
+        <v>480</v>
+      </c>
+      <c r="C74" s="13">
+        <v>120</v>
+      </c>
+      <c r="D74" s="13">
+        <v>180</v>
+      </c>
+      <c r="E74" s="13">
+        <v>210</v>
+      </c>
+      <c r="F74" s="13">
+        <v>60</v>
+      </c>
+      <c r="G74" s="13">
+        <v>1</v>
+      </c>
+      <c r="H74" s="13">
+        <v>60</v>
+      </c>
+      <c r="I74" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J74" s="14" t="str">
+        <v>1110</v>
+      </c>
+      <c r="J74" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K74" s="15"/>
-      <c r="L74" s="15"/>
-      <c r="M74" s="15"/>
-      <c r="N74" s="16"/>
+        <v>330</v>
+      </c>
+      <c r="K74" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L74" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M74" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N74" s="16" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A75" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="327" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{41791DD6-4198-47C1-B1DA-78C7E1E0DE39}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34E75FED-82D2-4E04-8B54-BC175A4292A6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="114">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4331,26 +4331,50 @@
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A75" s="8"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="13"/>
-      <c r="H75" s="13"/>
-      <c r="I75" s="14" t="str">
+      <c r="A75" s="8">
+        <v>46320</v>
+      </c>
+      <c r="B75" s="13">
+        <v>420</v>
+      </c>
+      <c r="C75" s="13">
+        <v>30</v>
+      </c>
+      <c r="D75" s="13">
+        <v>260</v>
+      </c>
+      <c r="E75" s="13">
+        <v>180</v>
+      </c>
+      <c r="F75" s="13">
+        <v>0</v>
+      </c>
+      <c r="G75" s="13">
+        <v>0</v>
+      </c>
+      <c r="H75" s="13">
+        <v>120</v>
+      </c>
+      <c r="I75" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J75" s="14" t="str">
+        <v>1010</v>
+      </c>
+      <c r="J75" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K75" s="15"/>
-      <c r="L75" s="15"/>
-      <c r="M75" s="15"/>
-      <c r="N75" s="16"/>
+        <v>430</v>
+      </c>
+      <c r="K75" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L75" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M75" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N75" s="16" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A76" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\OneDrive\Documents\Computer Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="339" documentId="13_ncr:1_{732F1569-5717-4D99-B03F-E6BC4F58C405}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34E75FED-82D2-4E04-8B54-BC175A4292A6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -380,6 +380,9 @@
   <si>
     <t>better than yesterday.</t>
   </si>
+  <si>
+    <t>today is a good day.</t>
+  </si>
 </sst>
 </file>
 
@@ -656,10 +659,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4377,26 +4376,50 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A76" s="8"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="13"/>
-      <c r="H76" s="13"/>
-      <c r="I76" s="14" t="str">
+      <c r="A76" s="8">
+        <v>46321</v>
+      </c>
+      <c r="B76" s="13">
+        <v>380</v>
+      </c>
+      <c r="C76" s="13">
+        <v>60</v>
+      </c>
+      <c r="D76" s="13">
+        <v>120</v>
+      </c>
+      <c r="E76" s="13">
+        <v>190</v>
+      </c>
+      <c r="F76" s="13">
+        <v>0</v>
+      </c>
+      <c r="G76" s="13">
+        <v>0</v>
+      </c>
+      <c r="H76" s="13">
+        <v>60</v>
+      </c>
+      <c r="I76" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J76" s="14" t="str">
+        <v>810</v>
+      </c>
+      <c r="J76" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K76" s="15"/>
-      <c r="L76" s="15"/>
-      <c r="M76" s="15"/>
-      <c r="N76" s="16"/>
+        <v>630</v>
+      </c>
+      <c r="K76" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L76" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M76" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N76" s="16" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A77" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sushma\OneDrive\Documents\Computer Application\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B734EF6-4408-4F8C-AC6B-1FB49AB961BF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4422,26 +4422,50 @@
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A77" s="8"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="13"/>
-      <c r="H77" s="13"/>
-      <c r="I77" s="14" t="str">
+      <c r="A77" s="8">
+        <v>46322</v>
+      </c>
+      <c r="B77" s="13">
+        <v>430</v>
+      </c>
+      <c r="C77" s="13">
+        <v>30</v>
+      </c>
+      <c r="D77" s="13">
+        <v>180</v>
+      </c>
+      <c r="E77" s="13">
+        <v>220</v>
+      </c>
+      <c r="F77" s="13">
+        <v>180</v>
+      </c>
+      <c r="G77" s="13">
+        <v>3</v>
+      </c>
+      <c r="H77" s="13">
+        <v>120</v>
+      </c>
+      <c r="I77" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J77" s="14" t="str">
+        <v>1160</v>
+      </c>
+      <c r="J77" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K77" s="15"/>
-      <c r="L77" s="15"/>
-      <c r="M77" s="15"/>
-      <c r="N77" s="16"/>
+        <v>280</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L77" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M77" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N77" s="16" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A78" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B734EF6-4408-4F8C-AC6B-1FB49AB961BF}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED6D9DFA-5660-43CF-BF38-B6EE84A0C0E7}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="116">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -383,6 +383,9 @@
   <si>
     <t>today is a good day.</t>
   </si>
+  <si>
+    <t>lovely day.</t>
+  </si>
 </sst>
 </file>
 
@@ -659,6 +662,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4468,26 +4475,50 @@
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A78" s="8"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="13"/>
-      <c r="H78" s="13"/>
-      <c r="I78" s="14" t="str">
+      <c r="A78" s="8">
+        <v>46323</v>
+      </c>
+      <c r="B78" s="13">
+        <v>380</v>
+      </c>
+      <c r="C78" s="13">
+        <v>120</v>
+      </c>
+      <c r="D78" s="13">
+        <v>120</v>
+      </c>
+      <c r="E78" s="13">
+        <v>180</v>
+      </c>
+      <c r="F78" s="13">
+        <v>240</v>
+      </c>
+      <c r="G78" s="13">
+        <v>4</v>
+      </c>
+      <c r="H78" s="13">
+        <v>180</v>
+      </c>
+      <c r="I78" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J78" s="14" t="str">
+        <v>1220</v>
+      </c>
+      <c r="J78" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K78" s="15"/>
-      <c r="L78" s="15"/>
-      <c r="M78" s="15"/>
-      <c r="N78" s="16"/>
+        <v>220</v>
+      </c>
+      <c r="K78" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="L78" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M78" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="N78" s="16" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A79" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ED6D9DFA-5660-43CF-BF38-B6EE84A0C0E7}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD00064A-F725-46E7-822D-DC238728914B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -385,6 +385,9 @@
   </si>
   <si>
     <t>lovely day.</t>
+  </si>
+  <si>
+    <t>Today I learned  new lessons.</t>
   </si>
 </sst>
 </file>
@@ -4521,26 +4524,50 @@
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A79" s="8"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="13"/>
-      <c r="H79" s="13"/>
-      <c r="I79" s="14" t="str">
+      <c r="A79" s="8">
+        <v>46324</v>
+      </c>
+      <c r="B79" s="13">
+        <v>420</v>
+      </c>
+      <c r="C79" s="13">
+        <v>40</v>
+      </c>
+      <c r="D79" s="13">
+        <v>120</v>
+      </c>
+      <c r="E79" s="13">
+        <v>180</v>
+      </c>
+      <c r="F79" s="13">
+        <v>300</v>
+      </c>
+      <c r="G79" s="13">
+        <v>5</v>
+      </c>
+      <c r="H79" s="13">
+        <v>120</v>
+      </c>
+      <c r="I79" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J79" s="14" t="str">
+        <v>1180</v>
+      </c>
+      <c r="J79" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K79" s="15"/>
-      <c r="L79" s="15"/>
-      <c r="M79" s="15"/>
-      <c r="N79" s="16"/>
+        <v>260</v>
+      </c>
+      <c r="K79" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="L79" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M79" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="N79" s="16" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A80" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD00064A-F725-46E7-822D-DC238728914B}"/>
+  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B025D71-B56C-48AE-9C2F-3C2779B991D1}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -388,6 +388,9 @@
   </si>
   <si>
     <t>Today I learned  new lessons.</t>
+  </si>
+  <si>
+    <t>Today I feel tried.</t>
   </si>
 </sst>
 </file>
@@ -4570,26 +4573,50 @@
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A80" s="8"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="13"/>
-      <c r="H80" s="13"/>
-      <c r="I80" s="14" t="str">
+      <c r="A80" s="8">
+        <v>46325</v>
+      </c>
+      <c r="B80" s="13">
+        <v>340</v>
+      </c>
+      <c r="C80" s="13">
+        <v>60</v>
+      </c>
+      <c r="D80" s="13">
+        <v>180</v>
+      </c>
+      <c r="E80" s="13">
+        <v>120</v>
+      </c>
+      <c r="F80" s="13">
+        <v>360</v>
+      </c>
+      <c r="G80" s="13">
+        <v>6</v>
+      </c>
+      <c r="H80" s="13">
+        <v>60</v>
+      </c>
+      <c r="I80" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J80" s="14" t="str">
+        <v>1120</v>
+      </c>
+      <c r="J80" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K80" s="15"/>
-      <c r="L80" s="15"/>
-      <c r="M80" s="15"/>
-      <c r="N80" s="16"/>
+        <v>320</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="L80" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M80" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N80" s="16" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A81" s="8"/>

--- a/12627062.xlsx
+++ b/12627062.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e613dd4f33c0853c/Documents/Computer Application/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="57" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B025D71-B56C-48AE-9C2F-3C2779B991D1}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="13_ncr:1_{78F238D0-41E4-412B-A7EE-B1D4158D2988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A27AE7D-449E-414D-8CE9-C73726D4C983}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -4619,26 +4619,50 @@
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A81" s="8"/>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="13"/>
-      <c r="H81" s="13"/>
-      <c r="I81" s="14" t="str">
+      <c r="A81" s="8">
+        <v>46326</v>
+      </c>
+      <c r="B81" s="13">
+        <v>420</v>
+      </c>
+      <c r="C81" s="13">
+        <v>45</v>
+      </c>
+      <c r="D81" s="13">
+        <v>120</v>
+      </c>
+      <c r="E81" s="13">
+        <v>120</v>
+      </c>
+      <c r="F81" s="13">
+        <v>180</v>
+      </c>
+      <c r="G81" s="13">
+        <v>3</v>
+      </c>
+      <c r="H81" s="13">
+        <v>60</v>
+      </c>
+      <c r="I81" s="14">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="J81" s="14" t="str">
+        <v>945</v>
+      </c>
+      <c r="J81" s="14">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="K81" s="15"/>
-      <c r="L81" s="15"/>
-      <c r="M81" s="15"/>
-      <c r="N81" s="16"/>
+        <v>495</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="L81" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="M81" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N81" s="16" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A82" s="8"/>
